--- a/data/k-props/2026-08-23.xlsx
+++ b/data/k-props/2026-08-23.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="97">
   <si>
     <t>date</t>
   </si>
@@ -148,39 +148,39 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Jose Soriano</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Carlos Rodon</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Jose Soriano</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Carlos Rodon</t>
-  </si>
-  <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
     <t>Jackson Kent</t>
   </si>
   <si>
@@ -274,28 +274,34 @@
     <t>Andrew Abbott</t>
   </si>
   <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>Jacob Waguespack</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>Brady Basso</t>
+  </si>
+  <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
     <t>Shane Drohan</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>Brady Basso</t>
-  </si>
-  <si>
-    <t>Sean Newcomb</t>
   </si>
 </sst>
 </file>
@@ -676,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -812,10 +818,10 @@
         <v>6.5</v>
       </c>
       <c r="D2">
-        <v>-122</v>
+        <v>-115</v>
       </c>
       <c r="E2">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -827,7 +833,7 @@
         <v>42</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S2" t="s">
         <v>42</v>
@@ -856,10 +862,10 @@
         <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-115</v>
+        <v>-148</v>
       </c>
       <c r="E3">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -904,10 +910,10 @@
         <v>45</v>
       </c>
       <c r="T3">
-        <v>0.1543</v>
+        <v>0.1861</v>
       </c>
       <c r="U3">
-        <v>0.1552</v>
+        <v>0.1849</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -916,10 +922,10 @@
         <v>0.2206</v>
       </c>
       <c r="X3">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y3">
-        <v>0.9645</v>
+        <v>1.0207</v>
       </c>
       <c r="AA3" t="s">
         <v>42</v>
@@ -928,7 +934,7 @@
         <v>42</v>
       </c>
       <c r="AD3">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="AE3" t="s">
         <v>46</v>
@@ -937,13 +943,13 @@
         <v>0.2436</v>
       </c>
       <c r="AG3">
-        <v>0.7049</v>
+        <v>0.8414</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -957,10 +963,10 @@
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-124</v>
+        <v>-132</v>
       </c>
       <c r="E4">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -1002,7 +1008,7 @@
         <v>0.379</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="T4">
         <v>0.2577</v>
@@ -1017,7 +1023,7 @@
         <v>0.2378</v>
       </c>
       <c r="X4">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y4">
         <v>1.0574</v>
@@ -1029,7 +1035,7 @@
         <v>42</v>
       </c>
       <c r="AD4">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="AE4" t="s">
         <v>46</v>
@@ -1038,13 +1044,13 @@
         <v>0.155</v>
       </c>
       <c r="AG4">
-        <v>1.1768</v>
+        <v>1.1649</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1052,16 +1058,16 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E5">
-        <v>-125</v>
+        <v>-135</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -1106,10 +1112,10 @@
         <v>45</v>
       </c>
       <c r="T5">
+        <v>0.1688</v>
+      </c>
+      <c r="U5">
         <v>0.1678</v>
-      </c>
-      <c r="U5">
-        <v>0.1665</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1118,10 +1124,10 @@
         <v>0.188</v>
       </c>
       <c r="X5">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y5">
-        <v>0.913</v>
+        <v>0.88</v>
       </c>
       <c r="AA5" t="s">
         <v>42</v>
@@ -1130,7 +1136,7 @@
         <v>42</v>
       </c>
       <c r="AD5">
-        <v>3.83</v>
+        <v>3.67</v>
       </c>
       <c r="AE5" t="s">
         <v>46</v>
@@ -1139,13 +1145,13 @@
         <v>0.2195</v>
       </c>
       <c r="AG5">
-        <v>0.7661</v>
+        <v>0.763</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.83</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1153,19 +1159,19 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>5.5</v>
       </c>
       <c r="D6">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E6">
         <v>-125</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>42</v>
@@ -1197,19 +1203,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>4.5</v>
       </c>
       <c r="D7">
-        <v>-146</v>
+        <v>-133</v>
       </c>
       <c r="E7">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
         <v>42</v>
@@ -1241,19 +1247,19 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>3.5</v>
       </c>
       <c r="D8">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E8">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>823827</v>
@@ -1292,7 +1298,7 @@
         <v>0.336</v>
       </c>
       <c r="S8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T8">
         <v>0.236</v>
@@ -1307,7 +1313,7 @@
         <v>0.2074</v>
       </c>
       <c r="X8">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y8">
         <v>1.0214</v>
@@ -1319,7 +1325,7 @@
         <v>42</v>
       </c>
       <c r="AD8">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="AE8" t="s">
         <v>46</v>
@@ -1328,13 +1334,13 @@
         <v>0.1606</v>
       </c>
       <c r="AG8">
-        <v>1.0776</v>
+        <v>1.0667</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1354,7 +1360,7 @@
         <v>-162</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
         <v>42</v>
@@ -1395,7 +1401,7 @@
         <v>-115</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -1437,7 +1443,7 @@
         <v>0.149</v>
       </c>
       <c r="S10" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T10">
         <v>0.177</v>
@@ -1452,7 +1458,7 @@
         <v>0.2286</v>
       </c>
       <c r="X10">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y10">
         <v>0.9715</v>
@@ -1464,7 +1470,7 @@
         <v>42</v>
       </c>
       <c r="AD10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="s">
         <v>46</v>
@@ -1473,13 +1479,13 @@
         <v>0.1856</v>
       </c>
       <c r="AG10">
-        <v>0.8082</v>
+        <v>0.8</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1493,7 +1499,7 @@
         <v>4.5</v>
       </c>
       <c r="D11">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E11">
         <v>-115</v>
@@ -1538,7 +1544,7 @@
         <v>0.306</v>
       </c>
       <c r="S11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T11">
         <v>0.248</v>
@@ -1553,7 +1559,7 @@
         <v>0.212</v>
       </c>
       <c r="X11">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y11">
         <v>1.0388</v>
@@ -1565,7 +1571,7 @@
         <v>42</v>
       </c>
       <c r="AD11">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="AE11" t="s">
         <v>46</v>
@@ -1574,13 +1580,13 @@
         <v>0.1734</v>
       </c>
       <c r="AG11">
-        <v>1.1325</v>
+        <v>1.1211</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1597,7 +1603,7 @@
         <v>115</v>
       </c>
       <c r="E12">
-        <v>-127</v>
+        <v>-131</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
@@ -1639,7 +1645,7 @@
         <v>0.385</v>
       </c>
       <c r="S12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T12">
         <v>0.2255</v>
@@ -1654,7 +1660,7 @@
         <v>0.2366</v>
       </c>
       <c r="X12">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y12">
         <v>1.0257</v>
@@ -1666,7 +1672,7 @@
         <v>42</v>
       </c>
       <c r="AD12">
-        <v>6.3</v>
+        <v>6.23</v>
       </c>
       <c r="AE12" t="s">
         <v>65</v>
@@ -1675,13 +1681,13 @@
         <v>0.2509</v>
       </c>
       <c r="AG12">
-        <v>1.0296</v>
+        <v>1.0191</v>
       </c>
       <c r="AH12">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>6.47</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1740,7 +1746,7 @@
         <v>0.32</v>
       </c>
       <c r="S13" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T13">
         <v>0.2342</v>
@@ -1755,7 +1761,7 @@
         <v>0.2443</v>
       </c>
       <c r="X13">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y13">
         <v>1.0256</v>
@@ -1767,7 +1773,7 @@
         <v>42</v>
       </c>
       <c r="AD13">
-        <v>5.41</v>
+        <v>5.35</v>
       </c>
       <c r="AE13" t="s">
         <v>46</v>
@@ -1776,13 +1782,13 @@
         <v>0.2431</v>
       </c>
       <c r="AG13">
-        <v>1.0694</v>
+        <v>1.0586</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>5.41</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1796,7 +1802,7 @@
         <v>3.5</v>
       </c>
       <c r="D14">
-        <v>-147</v>
+        <v>-149</v>
       </c>
       <c r="E14">
         <v>120</v>
@@ -1841,7 +1847,7 @@
         <v>0.361</v>
       </c>
       <c r="S14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T14">
         <v>0.2665</v>
@@ -1856,7 +1862,7 @@
         <v>0.2508</v>
       </c>
       <c r="X14">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y14">
         <v>1.0235</v>
@@ -1868,7 +1874,7 @@
         <v>42</v>
       </c>
       <c r="AD14">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="AE14" t="s">
         <v>46</v>
@@ -1877,13 +1883,13 @@
         <v>0.1867</v>
       </c>
       <c r="AG14">
-        <v>1.2171</v>
+        <v>1.2048</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1942,7 +1948,7 @@
         <v>0.375</v>
       </c>
       <c r="S15" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T15">
         <v>0.2063</v>
@@ -1957,7 +1963,7 @@
         <v>0.2355</v>
       </c>
       <c r="X15">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y15">
         <v>0.993</v>
@@ -1969,7 +1975,7 @@
         <v>42</v>
       </c>
       <c r="AD15">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="AE15" t="s">
         <v>46</v>
@@ -1978,13 +1984,13 @@
         <v>0.1899</v>
       </c>
       <c r="AG15">
-        <v>0.9422</v>
+        <v>0.9327</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2087,7 +2093,7 @@
         <v>0.367</v>
       </c>
       <c r="S17" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T17">
         <v>0.2277</v>
@@ -2102,7 +2108,7 @@
         <v>0.249</v>
       </c>
       <c r="X17">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y17">
         <v>1.0052</v>
@@ -2114,7 +2120,7 @@
         <v>42</v>
       </c>
       <c r="AD17">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
       <c r="AE17" t="s">
         <v>46</v>
@@ -2123,13 +2129,13 @@
         <v>0.2041</v>
       </c>
       <c r="AG17">
-        <v>1.0398</v>
+        <v>1.0293</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2188,7 +2194,7 @@
         <v>0.367</v>
       </c>
       <c r="S18" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T18">
         <v>0.2167</v>
@@ -2203,7 +2209,7 @@
         <v>0.2125</v>
       </c>
       <c r="X18">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y18">
         <v>0.9315</v>
@@ -2215,7 +2221,7 @@
         <v>42</v>
       </c>
       <c r="AD18">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AE18" t="s">
         <v>46</v>
@@ -2224,13 +2230,13 @@
         <v>0.1447</v>
       </c>
       <c r="AG18">
-        <v>0.9898</v>
+        <v>0.9798</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2244,10 +2250,10 @@
         <v>5.5</v>
       </c>
       <c r="D19">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E19">
-        <v>-172</v>
+        <v>-165</v>
       </c>
       <c r="F19" t="s">
         <v>76</v>
@@ -2289,7 +2295,7 @@
         <v>0.361</v>
       </c>
       <c r="S19" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T19">
         <v>0.2285</v>
@@ -2304,7 +2310,7 @@
         <v>0.2194</v>
       </c>
       <c r="X19">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y19">
         <v>0.9775</v>
@@ -2316,7 +2322,7 @@
         <v>42</v>
       </c>
       <c r="AD19">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AE19" t="s">
         <v>46</v>
@@ -2325,13 +2331,13 @@
         <v>0.2089</v>
       </c>
       <c r="AG19">
-        <v>1.0434</v>
+        <v>1.0328</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2345,10 +2351,10 @@
         <v>5.5</v>
       </c>
       <c r="D20">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="E20">
-        <v>-110</v>
+        <v>-106</v>
       </c>
       <c r="F20" t="s">
         <v>76</v>
@@ -2390,7 +2396,7 @@
         <v>0.363</v>
       </c>
       <c r="S20" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T20">
         <v>0.2425</v>
@@ -2405,7 +2411,7 @@
         <v>0.2418</v>
       </c>
       <c r="X20">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y20">
         <v>0.991</v>
@@ -2417,7 +2423,7 @@
         <v>42</v>
       </c>
       <c r="AD20">
-        <v>6.42</v>
+        <v>6.35</v>
       </c>
       <c r="AE20" t="s">
         <v>65</v>
@@ -2426,13 +2432,13 @@
         <v>0.253</v>
       </c>
       <c r="AG20">
-        <v>1.1073</v>
+        <v>1.096</v>
       </c>
       <c r="AH20">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.59</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2491,7 +2497,7 @@
         <v>0.24</v>
       </c>
       <c r="S21" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T21">
         <v>0.1949</v>
@@ -2506,7 +2512,7 @@
         <v>0.2592</v>
       </c>
       <c r="X21">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y21">
         <v>1.0078</v>
@@ -2518,7 +2524,7 @@
         <v>42</v>
       </c>
       <c r="AD21">
-        <v>5.98</v>
+        <v>5.92</v>
       </c>
       <c r="AE21" t="s">
         <v>46</v>
@@ -2527,13 +2533,13 @@
         <v>0.3175</v>
       </c>
       <c r="AG21">
-        <v>0.8901</v>
+        <v>0.8811</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.98</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2547,10 +2553,10 @@
         <v>2.5</v>
       </c>
       <c r="D22">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E22">
-        <v>-172</v>
+        <v>-179</v>
       </c>
       <c r="F22" t="s">
         <v>79</v>
@@ -2592,7 +2598,7 @@
         <v>0.19</v>
       </c>
       <c r="S22" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T22">
         <v>0.3057</v>
@@ -2607,7 +2613,7 @@
         <v>0.2075</v>
       </c>
       <c r="X22">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y22">
         <v>1.0048</v>
@@ -2619,7 +2625,7 @@
         <v>42</v>
       </c>
       <c r="AD22">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="AE22" t="s">
         <v>46</v>
@@ -2628,13 +2634,13 @@
         <v>0.2667</v>
       </c>
       <c r="AG22">
-        <v>1.3962</v>
+        <v>1.3821</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2648,7 +2654,7 @@
         <v>3.5</v>
       </c>
       <c r="D23">
-        <v>-106</v>
+        <v>-111</v>
       </c>
       <c r="E23">
         <v>-105</v>
@@ -2693,7 +2699,7 @@
         <v>0.363</v>
       </c>
       <c r="S23" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T23">
         <v>0.19</v>
@@ -2708,7 +2714,7 @@
         <v>0.2167</v>
       </c>
       <c r="X23">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y23">
         <v>0.9912</v>
@@ -2720,7 +2726,7 @@
         <v>42</v>
       </c>
       <c r="AD23">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AE23" t="s">
         <v>46</v>
@@ -2729,13 +2735,13 @@
         <v>0.1454</v>
       </c>
       <c r="AG23">
-        <v>0.8675</v>
+        <v>0.8587</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2752,7 +2758,7 @@
         <v>-136</v>
       </c>
       <c r="E24">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
         <v>82</v>
@@ -2794,7 +2800,7 @@
         <v>0.346</v>
       </c>
       <c r="S24" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T24">
         <v>0.1935</v>
@@ -2809,7 +2815,7 @@
         <v>0.2088</v>
       </c>
       <c r="X24">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y24">
         <v>0.9804</v>
@@ -2821,7 +2827,7 @@
         <v>42</v>
       </c>
       <c r="AD24">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="AE24" t="s">
         <v>46</v>
@@ -2830,13 +2836,13 @@
         <v>0.1966</v>
       </c>
       <c r="AG24">
-        <v>0.8838</v>
+        <v>0.8748</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2853,7 +2859,7 @@
         <v>-147</v>
       </c>
       <c r="E25">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" t="s">
         <v>85</v>
@@ -2895,7 +2901,7 @@
         <v>0.351</v>
       </c>
       <c r="S25" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T25">
         <v>0.3053</v>
@@ -2910,7 +2916,7 @@
         <v>0.2513</v>
       </c>
       <c r="X25">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y25">
         <v>1.0388</v>
@@ -2922,7 +2928,7 @@
         <v>42</v>
       </c>
       <c r="AD25">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="AE25" t="s">
         <v>46</v>
@@ -2931,13 +2937,13 @@
         <v>0.1605</v>
       </c>
       <c r="AG25">
-        <v>1.3943</v>
+        <v>1.3802</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2951,10 +2957,10 @@
         <v>3.5</v>
       </c>
       <c r="D26">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E26">
-        <v>-135</v>
+        <v>-132</v>
       </c>
       <c r="F26" t="s">
         <v>85</v>
@@ -2996,7 +3002,7 @@
         <v>0.381</v>
       </c>
       <c r="S26" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T26">
         <v>0.1637</v>
@@ -3011,7 +3017,7 @@
         <v>0.1752</v>
       </c>
       <c r="X26">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y26">
         <v>0.9178</v>
@@ -3023,7 +3029,7 @@
         <v>42</v>
       </c>
       <c r="AD26">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AE26" t="s">
         <v>46</v>
@@ -3032,13 +3038,13 @@
         <v>0.1664</v>
       </c>
       <c r="AG26">
-        <v>0.7477</v>
+        <v>0.7402</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3048,26 +3054,17 @@
       <c r="B27" t="s">
         <v>87</v>
       </c>
-      <c r="C27">
-        <v>4.5</v>
-      </c>
-      <c r="D27">
-        <v>-106</v>
-      </c>
-      <c r="E27">
-        <v>-112</v>
-      </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="G27">
-        <v>823745</v>
+        <v>823421</v>
       </c>
       <c r="H27" t="s">
         <v>44</v>
       </c>
       <c r="I27">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3076,46 +3073,46 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>0.2352</v>
+        <v>0.2779</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="Q27">
-        <v>0.2583</v>
+        <v>0.2927</v>
       </c>
       <c r="R27">
-        <v>0.375</v>
+        <v>0.381</v>
       </c>
       <c r="S27" t="s">
         <v>45</v>
       </c>
       <c r="T27">
-        <v>0.2353</v>
+        <v>0.2015</v>
       </c>
       <c r="U27">
-        <v>0.2307</v>
+        <v>0.1904</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>0.2101</v>
+        <v>0.1857</v>
       </c>
       <c r="X27">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y27">
-        <v>1.0121</v>
+        <v>0.9473</v>
       </c>
       <c r="AA27" t="s">
         <v>42</v>
@@ -3124,22 +3121,22 @@
         <v>42</v>
       </c>
       <c r="AD27">
-        <v>5.86</v>
+        <v>6.33</v>
       </c>
       <c r="AE27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AF27">
-        <v>0.2438</v>
+        <v>0.2835</v>
       </c>
       <c r="AG27">
-        <v>1.0746</v>
+        <v>0.911</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>5.86</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3147,28 +3144,19 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28">
-        <v>5.5</v>
-      </c>
-      <c r="D28">
-        <v>126</v>
-      </c>
-      <c r="E28">
-        <v>-140</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="G28">
-        <v>823745</v>
+        <v>823507</v>
       </c>
       <c r="H28" t="s">
         <v>44</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3177,46 +3165,46 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>0.2283</v>
+        <v>0.2353</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P28">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="Q28">
-        <v>0.2719</v>
+        <v>0.1875</v>
       </c>
       <c r="R28">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="S28" t="s">
         <v>45</v>
       </c>
       <c r="T28">
-        <v>0.2296</v>
+        <v>0.2594</v>
       </c>
       <c r="U28">
-        <v>0.2267</v>
+        <v>0.2717</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2148</v>
+        <v>0.2482</v>
       </c>
       <c r="X28">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y28">
-        <v>1.0069</v>
+        <v>1.0239</v>
       </c>
       <c r="AA28" t="s">
         <v>42</v>
@@ -3225,22 +3213,22 @@
         <v>42</v>
       </c>
       <c r="AD28">
-        <v>5.81</v>
+        <v>6.05</v>
       </c>
       <c r="AE28" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AF28">
-        <v>0.2442</v>
+        <v>0.2181</v>
       </c>
       <c r="AG28">
-        <v>1.0486</v>
+        <v>1.1724</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.81</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3248,19 +3236,19 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G29">
-        <v>823421</v>
+        <v>823507</v>
       </c>
       <c r="H29" t="s">
         <v>44</v>
       </c>
       <c r="I29">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3272,43 +3260,43 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.2779</v>
+        <v>0.2654</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="P29">
-        <v>4.16</v>
+        <v>4.19</v>
       </c>
       <c r="Q29">
-        <v>0.2927</v>
+        <v>0.271</v>
       </c>
       <c r="R29">
-        <v>0.381</v>
+        <v>0.349</v>
       </c>
       <c r="S29" t="s">
         <v>45</v>
       </c>
       <c r="T29">
-        <v>0.1954</v>
+        <v>0.1935</v>
       </c>
       <c r="U29">
-        <v>0.1961</v>
+        <v>0.1712</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>0.1857</v>
+        <v>0.2104</v>
       </c>
       <c r="X29">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y29">
-        <v>0.9827</v>
+        <v>0.943</v>
       </c>
       <c r="AA29" t="s">
         <v>42</v>
@@ -3317,22 +3305,22 @@
         <v>42</v>
       </c>
       <c r="AD29">
-        <v>6.44</v>
+        <v>4.65</v>
       </c>
       <c r="AE29" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF29">
-        <v>0.2835</v>
+        <v>0.2674</v>
       </c>
       <c r="AG29">
-        <v>0.8924</v>
+        <v>0.8746</v>
       </c>
       <c r="AH29">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>6.61</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3340,22 +3328,22 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30">
+        <v>824071</v>
+      </c>
+      <c r="H30" t="s">
         <v>91</v>
       </c>
-      <c r="F30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30">
-        <v>823507</v>
-      </c>
-      <c r="H30" t="s">
-        <v>44</v>
-      </c>
       <c r="I30">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -3364,43 +3352,31 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.2353</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>112</v>
+        <v>0.1495</v>
       </c>
       <c r="P30">
-        <v>4.15</v>
-      </c>
-      <c r="Q30">
-        <v>0.1875</v>
-      </c>
-      <c r="R30">
-        <v>0.359</v>
+        <v>3.87</v>
       </c>
       <c r="S30" t="s">
         <v>45</v>
       </c>
       <c r="T30">
-        <v>0.256</v>
+        <v>0.2083</v>
       </c>
       <c r="U30">
-        <v>0.2681</v>
+        <v>0.1827</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2482</v>
+        <v>0.2078</v>
       </c>
       <c r="X30">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y30">
-        <v>1.011</v>
+        <v>0.8901</v>
       </c>
       <c r="AA30" t="s">
         <v>42</v>
@@ -3409,22 +3385,22 @@
         <v>42</v>
       </c>
       <c r="AD30">
-        <v>5.96</v>
+        <v>2.18</v>
       </c>
       <c r="AE30" t="s">
         <v>46</v>
       </c>
       <c r="AF30">
-        <v>0.2181</v>
+        <v>0.1495</v>
       </c>
       <c r="AG30">
-        <v>1.1691</v>
+        <v>0.9414</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>5.96</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3435,19 +3411,19 @@
         <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G31">
-        <v>823507</v>
+        <v>824150</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -3456,43 +3432,43 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0.2654</v>
+        <v>0.19</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="P31">
-        <v>4.19</v>
+        <v>4.35</v>
       </c>
       <c r="Q31">
-        <v>0.271</v>
+        <v>0.2105</v>
       </c>
       <c r="R31">
-        <v>0.349</v>
+        <v>0.087</v>
       </c>
       <c r="S31" t="s">
         <v>45</v>
       </c>
       <c r="T31">
-        <v>0.2001</v>
+        <v>0.218</v>
       </c>
       <c r="U31">
-        <v>0.1869</v>
+        <v>0.2101</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
-        <v>0.2104</v>
+        <v>0.2091</v>
       </c>
       <c r="X31">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y31">
-        <v>0.9817</v>
+        <v>0.9618</v>
       </c>
       <c r="AA31" t="s">
         <v>42</v>
@@ -3501,22 +3477,22 @@
         <v>42</v>
       </c>
       <c r="AD31">
-        <v>5.06</v>
+        <v>1.84</v>
       </c>
       <c r="AE31" t="s">
         <v>46</v>
       </c>
       <c r="AF31">
-        <v>0.2674</v>
+        <v>0.1918</v>
       </c>
       <c r="AG31">
-        <v>0.9138</v>
+        <v>0.9854</v>
       </c>
       <c r="AH31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>5.06</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3527,16 +3503,16 @@
         <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G32">
-        <v>824150</v>
+        <v>824558</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
       </c>
       <c r="I32">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -3548,43 +3524,43 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0.19</v>
+        <v>0.2261</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O32">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P32">
-        <v>4.35</v>
+        <v>4.04</v>
       </c>
       <c r="Q32">
-        <v>0.2105</v>
+        <v>0.2857</v>
       </c>
       <c r="R32">
-        <v>0.087</v>
+        <v>0.095</v>
       </c>
       <c r="S32" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T32">
-        <v>0.2158</v>
+        <v>0.2104</v>
       </c>
       <c r="U32">
-        <v>0.2084</v>
+        <v>0.2287</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>0.2091</v>
+        <v>0.2302</v>
       </c>
       <c r="X32">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y32">
-        <v>0.9924</v>
+        <v>0.9949</v>
       </c>
       <c r="AA32" t="s">
         <v>42</v>
@@ -3593,22 +3569,22 @@
         <v>42</v>
       </c>
       <c r="AD32">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="s">
         <v>46</v>
       </c>
       <c r="AF32">
-        <v>0.1918</v>
+        <v>0.2318</v>
       </c>
       <c r="AG32">
-        <v>0.9856</v>
+        <v>0.9512</v>
       </c>
       <c r="AH32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3618,65 +3594,74 @@
       <c r="B33" t="s">
         <v>94</v>
       </c>
+      <c r="C33">
+        <v>5.5</v>
+      </c>
+      <c r="D33">
+        <v>126</v>
+      </c>
+      <c r="E33">
+        <v>-140</v>
+      </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="G33">
-        <v>824558</v>
+        <v>823745</v>
       </c>
       <c r="H33" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I33">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>0.2261</v>
+        <v>0.2283</v>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="P33">
-        <v>4.04</v>
+        <v>4.17</v>
       </c>
       <c r="Q33">
-        <v>0.2857</v>
+        <v>0.2719</v>
       </c>
       <c r="R33">
-        <v>0.095</v>
+        <v>0.363</v>
       </c>
       <c r="S33" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T33">
-        <v>0.2104</v>
+        <v>0.2296</v>
       </c>
       <c r="U33">
-        <v>0.2287</v>
+        <v>0.2267</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>0.2302</v>
+        <v>0.2148</v>
       </c>
       <c r="X33">
-        <v>0.219</v>
+        <v>0.2212</v>
       </c>
       <c r="Y33">
-        <v>0.9949</v>
+        <v>1.0069</v>
       </c>
       <c r="AA33" t="s">
         <v>42</v>
@@ -3685,22 +3670,123 @@
         <v>42</v>
       </c>
       <c r="AD33">
-        <v>1.89</v>
+        <v>5.75</v>
       </c>
       <c r="AE33" t="s">
         <v>46</v>
       </c>
       <c r="AF33">
-        <v>0.2318</v>
+        <v>0.2442</v>
       </c>
       <c r="AG33">
-        <v>0.9609</v>
+        <v>1.038</v>
       </c>
       <c r="AH33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>1.89</v>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34">
+        <v>4.5</v>
+      </c>
+      <c r="D34">
+        <v>-106</v>
+      </c>
+      <c r="E34">
+        <v>-112</v>
+      </c>
+      <c r="F34" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34">
+        <v>823745</v>
+      </c>
+      <c r="H34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34">
+        <v>5.3</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>6</v>
+      </c>
+      <c r="M34">
+        <v>0.2352</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34">
+        <v>120</v>
+      </c>
+      <c r="P34">
+        <v>4.2</v>
+      </c>
+      <c r="Q34">
+        <v>0.2583</v>
+      </c>
+      <c r="R34">
+        <v>0.375</v>
+      </c>
+      <c r="S34" t="s">
+        <v>55</v>
+      </c>
+      <c r="T34">
+        <v>0.2353</v>
+      </c>
+      <c r="U34">
+        <v>0.2307</v>
+      </c>
+      <c r="V34">
+        <v>9</v>
+      </c>
+      <c r="W34">
+        <v>0.2101</v>
+      </c>
+      <c r="X34">
+        <v>0.2212</v>
+      </c>
+      <c r="Y34">
+        <v>1.0121</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD34">
+        <v>5.8</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF34">
+        <v>0.2438</v>
+      </c>
+      <c r="AG34">
+        <v>1.0637</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-23.xlsx
+++ b/data/k-props/2026-08-23.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -133,175 +133,178 @@
     <t>08/23/2026</t>
   </si>
   <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Jacob Waguespack</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Brady Basso</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Cristian Javier</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Yusei Kikuchi</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Blake Snell</t>
+  </si>
+  <si>
+    <t>Shota Imanaga</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Shane Drohan</t>
+  </si>
+  <si>
     <t>Cristopher Sanchez</t>
   </si>
   <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
     <t>Jose Soriano</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
     <t>Carlos Rodon</t>
   </si>
   <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
     <t>Jackson Kent</t>
   </si>
   <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Cristian Javier</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Nolan McLean</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Yusei Kikuchi</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
     <t>Matt Wilkinson</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Shota Imanaga</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>Jacob Waguespack</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Brady Basso</t>
-  </si>
-  <si>
-    <t>Sean Newcomb</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Shane Drohan</t>
   </si>
 </sst>
 </file>
@@ -815,40 +818,97 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D2">
-        <v>-115</v>
+        <v>-132</v>
       </c>
       <c r="E2">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
-        <v>42</v>
+      <c r="G2">
+        <v>824799</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
+      <c r="I2">
+        <v>5.9</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
       <c r="L2">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>0.1446</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <v>122</v>
+      </c>
+      <c r="P2">
+        <v>4.05</v>
+      </c>
+      <c r="Q2">
+        <v>0.1721</v>
+      </c>
+      <c r="R2">
+        <v>0.379</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T2">
+        <v>0.2577</v>
+      </c>
+      <c r="U2">
+        <v>0.2466</v>
+      </c>
+      <c r="V2">
+        <v>9</v>
+      </c>
+      <c r="W2">
+        <v>0.2378</v>
+      </c>
+      <c r="X2">
+        <v>0.2227</v>
+      </c>
+      <c r="Y2">
+        <v>1.0574</v>
       </c>
       <c r="AA2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD2">
+        <v>4.54</v>
       </c>
       <c r="AE2" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF2">
+        <v>0.155</v>
+      </c>
+      <c r="AG2">
+        <v>1.1569</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>4.54</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -856,28 +916,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-148</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>132</v>
+        <v>-135</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3">
-        <v>823421</v>
+        <v>824799</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -886,70 +946,70 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>0.2151</v>
+        <v>0.2119</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="P3">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="Q3">
-        <v>0.2963</v>
+        <v>0.2328</v>
       </c>
       <c r="R3">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="S3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T3">
-        <v>0.1861</v>
+        <v>0.1688</v>
       </c>
       <c r="U3">
-        <v>0.1849</v>
+        <v>0.1678</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2206</v>
+        <v>0.188</v>
       </c>
       <c r="X3">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y3">
-        <v>1.0207</v>
+        <v>0.88</v>
       </c>
       <c r="AA3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD3">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AE3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2436</v>
+        <v>0.2195</v>
       </c>
       <c r="AG3">
-        <v>0.8414</v>
+        <v>0.7578</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -963,22 +1023,22 @@
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-132</v>
+        <v>-148</v>
       </c>
       <c r="E4">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
       <c r="G4">
-        <v>824799</v>
+        <v>823421</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -987,70 +1047,70 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1446</v>
+        <v>0.2151</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="P4">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="Q4">
-        <v>0.1721</v>
+        <v>0.2963</v>
       </c>
       <c r="R4">
-        <v>0.379</v>
+        <v>0.351</v>
       </c>
       <c r="S4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2577</v>
+        <v>0.1861</v>
       </c>
       <c r="U4">
-        <v>0.2466</v>
+        <v>0.1849</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2378</v>
+        <v>0.2206</v>
       </c>
       <c r="X4">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y4">
-        <v>1.0574</v>
+        <v>1.0207</v>
       </c>
       <c r="AA4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="AE4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.155</v>
+        <v>0.2436</v>
       </c>
       <c r="AG4">
-        <v>1.1649</v>
+        <v>0.8356</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1060,26 +1120,17 @@
       <c r="B5" t="s">
         <v>49</v>
       </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-      <c r="D5">
-        <v>124</v>
-      </c>
-      <c r="E5">
-        <v>-135</v>
-      </c>
       <c r="F5" t="s">
         <v>48</v>
       </c>
       <c r="G5">
-        <v>824799</v>
+        <v>823421</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1088,70 +1139,70 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.2119</v>
+        <v>0.2779</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="P5">
-        <v>4.28</v>
+        <v>4.16</v>
       </c>
       <c r="Q5">
-        <v>0.2328</v>
+        <v>0.2927</v>
       </c>
       <c r="R5">
-        <v>0.367</v>
+        <v>0.381</v>
       </c>
       <c r="S5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1688</v>
+        <v>0.2015</v>
       </c>
       <c r="U5">
-        <v>0.1678</v>
+        <v>0.1904</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>0.188</v>
+        <v>0.1857</v>
       </c>
       <c r="X5">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y5">
-        <v>0.88</v>
+        <v>0.9473</v>
       </c>
       <c r="AA5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.67</v>
+        <v>6.29</v>
       </c>
       <c r="AE5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>0.2195</v>
+        <v>0.2835</v>
       </c>
       <c r="AG5">
-        <v>0.763</v>
+        <v>0.9048</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.67</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1159,43 +1210,91 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-      <c r="D6">
-        <v>110</v>
-      </c>
-      <c r="E6">
-        <v>-125</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="G6">
+        <v>823507</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
+      <c r="I6">
+        <v>5.6</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
       <c r="L6">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0.2353</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>112</v>
+      </c>
+      <c r="P6">
+        <v>4.15</v>
+      </c>
+      <c r="Q6">
+        <v>0.1875</v>
+      </c>
+      <c r="R6">
+        <v>0.359</v>
       </c>
       <c r="S6" t="s">
-        <v>42</v>
-      </c>
-      <c r="V6" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T6">
+        <v>0.2594</v>
+      </c>
+      <c r="U6">
+        <v>0.2717</v>
+      </c>
+      <c r="V6">
+        <v>9</v>
+      </c>
+      <c r="W6">
+        <v>0.2482</v>
+      </c>
+      <c r="X6">
+        <v>0.2227</v>
+      </c>
+      <c r="Y6">
+        <v>1.0239</v>
       </c>
       <c r="AA6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC6" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD6">
+        <v>6.01</v>
       </c>
       <c r="AE6" t="s">
-        <v>42</v>
+        <v>50</v>
+      </c>
+      <c r="AF6">
+        <v>0.2181</v>
+      </c>
+      <c r="AG6">
+        <v>1.1644</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>6.01</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1203,43 +1302,91 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
         <v>52</v>
       </c>
-      <c r="C7">
-        <v>4.5</v>
-      </c>
-      <c r="D7">
-        <v>-133</v>
-      </c>
-      <c r="E7">
-        <v>114</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
+      <c r="G7">
+        <v>823507</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
       <c r="L7">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0.2654</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <v>107</v>
+      </c>
+      <c r="P7">
+        <v>4.19</v>
+      </c>
+      <c r="Q7">
+        <v>0.271</v>
+      </c>
+      <c r="R7">
+        <v>0.349</v>
       </c>
       <c r="S7" t="s">
-        <v>42</v>
-      </c>
-      <c r="V7" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T7">
+        <v>0.1935</v>
+      </c>
+      <c r="U7">
+        <v>0.1712</v>
+      </c>
+      <c r="V7">
+        <v>9</v>
+      </c>
+      <c r="W7">
+        <v>0.2104</v>
+      </c>
+      <c r="X7">
+        <v>0.2227</v>
+      </c>
+      <c r="Y7">
+        <v>0.943</v>
       </c>
       <c r="AA7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC7" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD7">
+        <v>4.62</v>
       </c>
       <c r="AE7" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF7">
+        <v>0.2674</v>
+      </c>
+      <c r="AG7">
+        <v>0.8686</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>4.62</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1247,7 +1394,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1259,13 +1406,13 @@
         <v>-115</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>823827</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I8">
         <v>5.1</v>
@@ -1298,13 +1445,13 @@
         <v>0.336</v>
       </c>
       <c r="S8" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.236</v>
+        <v>0.2055</v>
       </c>
       <c r="U8">
-        <v>0.2366</v>
+        <v>0.2052</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1313,34 +1460,34 @@
         <v>0.2074</v>
       </c>
       <c r="X8">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y8">
-        <v>1.0214</v>
+        <v>0.9665</v>
       </c>
       <c r="AA8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="AE8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF8">
         <v>0.1606</v>
       </c>
       <c r="AG8">
-        <v>1.0667</v>
+        <v>0.9226</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1350,41 +1497,77 @@
       <c r="B9" t="s">
         <v>56</v>
       </c>
-      <c r="C9">
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>824071</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9">
         <v>4.5</v>
       </c>
-      <c r="D9">
-        <v>145</v>
-      </c>
-      <c r="E9">
-        <v>-162</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0.1495</v>
+      </c>
+      <c r="P9">
+        <v>3.87</v>
       </c>
       <c r="S9" t="s">
-        <v>42</v>
-      </c>
-      <c r="V9" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T9">
+        <v>0.2106</v>
+      </c>
+      <c r="U9">
+        <v>0.1859</v>
+      </c>
+      <c r="V9">
+        <v>9</v>
+      </c>
+      <c r="W9">
+        <v>0.2078</v>
+      </c>
+      <c r="X9">
+        <v>0.2227</v>
+      </c>
+      <c r="Y9">
+        <v>0.88</v>
       </c>
       <c r="AA9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC9" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD9">
+        <v>2.17</v>
       </c>
       <c r="AE9" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF9">
+        <v>0.1495</v>
+      </c>
+      <c r="AG9">
+        <v>0.9454</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>2.17</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1392,7 +1575,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>2.5</v>
@@ -1404,13 +1587,13 @@
         <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>824071</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I10">
         <v>2.7</v>
@@ -1443,13 +1626,13 @@
         <v>0.149</v>
       </c>
       <c r="S10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.177</v>
+        <v>0.2021</v>
       </c>
       <c r="U10">
-        <v>0.1883</v>
+        <v>0.1935</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1458,34 +1641,34 @@
         <v>0.2286</v>
       </c>
       <c r="X10">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y10">
-        <v>0.9715</v>
+        <v>0.987</v>
       </c>
       <c r="AA10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD10">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AE10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF10">
         <v>0.1856</v>
       </c>
       <c r="AG10">
-        <v>0.8</v>
+        <v>0.9072</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1493,100 +1676,91 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11">
-        <v>4.5</v>
-      </c>
-      <c r="D11">
-        <v>106</v>
-      </c>
-      <c r="E11">
-        <v>-115</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>824150</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I11">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0.1796</v>
+        <v>0.19</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="P11">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q11">
-        <v>0.1591</v>
+        <v>0.2105</v>
       </c>
       <c r="R11">
-        <v>0.306</v>
+        <v>0.087</v>
       </c>
       <c r="S11" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.248</v>
+        <v>0.218</v>
       </c>
       <c r="U11">
-        <v>0.2202</v>
+        <v>0.2101</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.212</v>
+        <v>0.2091</v>
       </c>
       <c r="X11">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y11">
-        <v>1.0388</v>
+        <v>0.9618</v>
       </c>
       <c r="AA11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1734</v>
+        <v>0.1918</v>
       </c>
       <c r="AG11">
-        <v>1.1211</v>
+        <v>0.9786</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.62</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1597,25 +1771,25 @@
         <v>63</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D12">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E12">
-        <v>-131</v>
+        <v>-115</v>
       </c>
       <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>824150</v>
+      </c>
+      <c r="H12" t="s">
         <v>64</v>
       </c>
-      <c r="G12">
-        <v>824558</v>
-      </c>
-      <c r="H12" t="s">
-        <v>44</v>
-      </c>
       <c r="I12">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1627,67 +1801,67 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.2727</v>
+        <v>0.1796</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="P12">
-        <v>4.16</v>
+        <v>4.6</v>
       </c>
       <c r="Q12">
-        <v>0.216</v>
+        <v>0.1591</v>
       </c>
       <c r="R12">
-        <v>0.385</v>
+        <v>0.306</v>
       </c>
       <c r="S12" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2255</v>
+        <v>0.2037</v>
       </c>
       <c r="U12">
-        <v>0.2446</v>
+        <v>0.2147</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2366</v>
+        <v>0.212</v>
       </c>
       <c r="X12">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y12">
-        <v>1.0257</v>
+        <v>1.0766</v>
       </c>
       <c r="AA12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD12">
-        <v>6.23</v>
+        <v>3.06</v>
       </c>
       <c r="AE12" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.2509</v>
+        <v>0.1734</v>
       </c>
       <c r="AG12">
-        <v>1.0191</v>
+        <v>0.9144</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>6.23</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1695,28 +1869,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13">
+        <v>6.5</v>
+      </c>
+      <c r="D13">
+        <v>115</v>
+      </c>
+      <c r="E13">
+        <v>-131</v>
+      </c>
+      <c r="F13" t="s">
         <v>66</v>
       </c>
-      <c r="C13">
-        <v>4.5</v>
-      </c>
-      <c r="D13">
-        <v>-110</v>
-      </c>
-      <c r="E13">
-        <v>102</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
       <c r="G13">
-        <v>822856</v>
+        <v>824558</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I13">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1725,70 +1899,70 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2324</v>
+        <v>0.2727</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="P13">
-        <v>4.58</v>
+        <v>4.16</v>
       </c>
       <c r="Q13">
-        <v>0.266</v>
+        <v>0.216</v>
       </c>
       <c r="R13">
-        <v>0.32</v>
+        <v>0.385</v>
       </c>
       <c r="S13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2342</v>
+        <v>0.2516</v>
       </c>
       <c r="U13">
-        <v>0.2346</v>
+        <v>0.2537</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2443</v>
+        <v>0.2366</v>
       </c>
       <c r="X13">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y13">
-        <v>1.0256</v>
+        <v>1.0565</v>
       </c>
       <c r="AA13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD13">
-        <v>5.35</v>
+        <v>7.11</v>
       </c>
       <c r="AE13" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="AF13">
-        <v>0.2431</v>
+        <v>0.2509</v>
       </c>
       <c r="AG13">
-        <v>1.0586</v>
+        <v>1.1295</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>5.35</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1798,98 +1972,89 @@
       <c r="B14" t="s">
         <v>68</v>
       </c>
-      <c r="C14">
-        <v>3.5</v>
-      </c>
-      <c r="D14">
-        <v>-149</v>
-      </c>
-      <c r="E14">
-        <v>120</v>
-      </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G14">
-        <v>822856</v>
+        <v>824558</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>0.1672</v>
+        <v>0.2261</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="P14">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="Q14">
-        <v>0.2212</v>
+        <v>0.2857</v>
       </c>
       <c r="R14">
-        <v>0.361</v>
+        <v>0.095</v>
       </c>
       <c r="S14" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2665</v>
+        <v>0.1795</v>
       </c>
       <c r="U14">
-        <v>0.2531</v>
+        <v>0.2127</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2508</v>
+        <v>0.2302</v>
       </c>
       <c r="X14">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y14">
-        <v>1.0235</v>
+        <v>0.9312</v>
       </c>
       <c r="AA14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.72</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1867</v>
+        <v>0.2318</v>
       </c>
       <c r="AG14">
-        <v>1.2048</v>
+        <v>0.8059</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.72</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1903,22 +2068,22 @@
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-122</v>
+        <v>-110</v>
       </c>
       <c r="E15">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
         <v>70</v>
       </c>
       <c r="G15">
-        <v>824720</v>
+        <v>822856</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1930,67 +2095,67 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1889</v>
+        <v>0.2324</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>4.58</v>
       </c>
       <c r="Q15">
-        <v>0.1917</v>
+        <v>0.266</v>
       </c>
       <c r="R15">
-        <v>0.375</v>
+        <v>0.32</v>
       </c>
       <c r="S15" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T15">
-        <v>0.2063</v>
+        <v>0.2342</v>
       </c>
       <c r="U15">
-        <v>0.2058</v>
+        <v>0.2346</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0.2355</v>
+        <v>0.2443</v>
       </c>
       <c r="X15">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y15">
-        <v>0.993</v>
+        <v>1.0256</v>
       </c>
       <c r="AA15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.06</v>
+        <v>5.32</v>
       </c>
       <c r="AE15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.1899</v>
+        <v>0.2431</v>
       </c>
       <c r="AG15">
-        <v>0.9327</v>
+        <v>1.0513</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.06</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -1998,43 +2163,100 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
-        <v>-110</v>
+        <v>-149</v>
       </c>
       <c r="E16">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="G16" t="s">
-        <v>42</v>
+      <c r="G16">
+        <v>822856</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
+      <c r="I16">
+        <v>4.9</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
       <c r="L16">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <v>0.1672</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16">
+        <v>113</v>
+      </c>
+      <c r="P16">
+        <v>4.16</v>
+      </c>
+      <c r="Q16">
+        <v>0.2212</v>
+      </c>
+      <c r="R16">
+        <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>42</v>
-      </c>
-      <c r="V16" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T16">
+        <v>0.2953</v>
+      </c>
+      <c r="U16">
+        <v>0.2748</v>
+      </c>
+      <c r="V16">
+        <v>9</v>
+      </c>
+      <c r="W16">
+        <v>0.2508</v>
+      </c>
+      <c r="X16">
+        <v>0.2227</v>
+      </c>
+      <c r="Y16">
+        <v>1.0756</v>
       </c>
       <c r="AA16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC16" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD16">
+        <v>5.45</v>
       </c>
       <c r="AE16" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF16">
+        <v>0.1867</v>
+      </c>
+      <c r="AG16">
+        <v>1.3256</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>5.45</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2042,7 +2264,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2054,13 +2276,13 @@
         <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>824315</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I17">
         <v>5.8</v>
@@ -2093,7 +2315,7 @@
         <v>0.367</v>
       </c>
       <c r="S17" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T17">
         <v>0.2277</v>
@@ -2108,34 +2330,34 @@
         <v>0.249</v>
       </c>
       <c r="X17">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y17">
         <v>1.0052</v>
       </c>
       <c r="AA17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="AE17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF17">
         <v>0.2041</v>
       </c>
       <c r="AG17">
-        <v>1.0293</v>
+        <v>1.0222</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2143,7 +2365,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>2.5</v>
@@ -2155,13 +2377,13 @@
         <v>-110</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>824315</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>5.4</v>
@@ -2194,13 +2416,13 @@
         <v>0.367</v>
       </c>
       <c r="S18" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2167</v>
+        <v>0.1845</v>
       </c>
       <c r="U18">
-        <v>0.192</v>
+        <v>0.1869</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2209,34 +2431,34 @@
         <v>0.2125</v>
       </c>
       <c r="X18">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y18">
-        <v>0.9315</v>
+        <v>0.88</v>
       </c>
       <c r="AA18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="AE18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF18">
         <v>0.1447</v>
       </c>
       <c r="AG18">
-        <v>0.9798</v>
+        <v>0.8285</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2244,28 +2466,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>132</v>
+        <v>-122</v>
       </c>
       <c r="E19">
-        <v>-165</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19">
-        <v>823099</v>
+        <v>824720</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2277,67 +2499,67 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2458</v>
+        <v>0.1889</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>0.1416</v>
+        <v>0.1917</v>
       </c>
       <c r="R19">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="S19" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2285</v>
+        <v>0.265</v>
       </c>
       <c r="U19">
-        <v>0.2264</v>
+        <v>0.2278</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2194</v>
+        <v>0.2355</v>
       </c>
       <c r="X19">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y19">
-        <v>0.9775</v>
+        <v>1.0136</v>
       </c>
       <c r="AA19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.7</v>
+        <v>5.28</v>
       </c>
       <c r="AE19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2089</v>
+        <v>0.1899</v>
       </c>
       <c r="AG19">
-        <v>1.0328</v>
+        <v>1.1898</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.7</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2345,100 +2567,100 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D20">
-        <v>-108</v>
+        <v>140</v>
       </c>
       <c r="E20">
-        <v>-106</v>
+        <v>-179</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G20">
-        <v>823099</v>
+        <v>823909</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I20">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>0.2422</v>
+        <v>0.2544</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="P20">
-        <v>4.03</v>
+        <v>4.12</v>
       </c>
       <c r="Q20">
-        <v>0.2719</v>
+        <v>0.3191</v>
       </c>
       <c r="R20">
-        <v>0.363</v>
+        <v>0.19</v>
       </c>
       <c r="S20" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T20">
-        <v>0.2425</v>
+        <v>0.3057</v>
       </c>
       <c r="U20">
-        <v>0.216</v>
+        <v>0.2029</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2418</v>
+        <v>0.2075</v>
       </c>
       <c r="X20">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y20">
-        <v>0.991</v>
+        <v>1.0048</v>
       </c>
       <c r="AA20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.35</v>
+        <v>3.64</v>
       </c>
       <c r="AE20" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.253</v>
+        <v>0.2667</v>
       </c>
       <c r="AG20">
-        <v>1.096</v>
+        <v>1.3726</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>6.35</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2446,7 +2668,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>8.5</v>
@@ -2464,7 +2686,7 @@
         <v>823909</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2497,7 +2719,7 @@
         <v>0.24</v>
       </c>
       <c r="S21" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T21">
         <v>0.1949</v>
@@ -2512,34 +2734,34 @@
         <v>0.2592</v>
       </c>
       <c r="X21">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y21">
         <v>1.0078</v>
       </c>
       <c r="AA21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.92</v>
+        <v>5.88</v>
       </c>
       <c r="AE21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF21">
         <v>0.3175</v>
       </c>
       <c r="AG21">
-        <v>0.8811</v>
+        <v>0.8751</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.92</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2547,100 +2769,100 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>140</v>
+        <v>-108</v>
       </c>
       <c r="E22">
-        <v>-179</v>
+        <v>-106</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G22">
-        <v>823909</v>
+        <v>823099</v>
       </c>
       <c r="H22" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I22">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2544</v>
+        <v>0.2422</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="P22">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="Q22">
-        <v>0.3191</v>
+        <v>0.2719</v>
       </c>
       <c r="R22">
-        <v>0.19</v>
+        <v>0.363</v>
       </c>
       <c r="S22" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T22">
-        <v>0.3057</v>
+        <v>0.2425</v>
       </c>
       <c r="U22">
-        <v>0.2029</v>
+        <v>0.216</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2075</v>
+        <v>0.2418</v>
       </c>
       <c r="X22">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y22">
-        <v>1.0048</v>
+        <v>0.991</v>
       </c>
       <c r="AA22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.66</v>
+        <v>6.31</v>
       </c>
       <c r="AE22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF22">
-        <v>0.2667</v>
+        <v>0.253</v>
       </c>
       <c r="AG22">
-        <v>1.3821</v>
+        <v>1.0885</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>3.66</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2648,28 +2870,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C23">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>-111</v>
+        <v>132</v>
       </c>
       <c r="E23">
-        <v>-105</v>
+        <v>-165</v>
       </c>
       <c r="F23" t="s">
         <v>82</v>
       </c>
       <c r="G23">
-        <v>823258</v>
+        <v>823099</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2681,67 +2903,67 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1632</v>
+        <v>0.2458</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P23">
-        <v>4.21</v>
+        <v>3.95</v>
       </c>
       <c r="Q23">
-        <v>0.114</v>
+        <v>0.1416</v>
       </c>
       <c r="R23">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="S23" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T23">
-        <v>0.19</v>
+        <v>0.2285</v>
       </c>
       <c r="U23">
-        <v>0.1911</v>
+        <v>0.2264</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2167</v>
+        <v>0.2194</v>
       </c>
       <c r="X23">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y23">
-        <v>0.9912</v>
+        <v>0.9775</v>
       </c>
       <c r="AA23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.83</v>
+        <v>4.67</v>
       </c>
       <c r="AE23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.1454</v>
+        <v>0.2089</v>
       </c>
       <c r="AG23">
-        <v>0.8587</v>
+        <v>1.0258</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.83</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2749,28 +2971,28 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>3.5</v>
       </c>
       <c r="D24">
-        <v>-136</v>
+        <v>-111</v>
       </c>
       <c r="E24">
-        <v>118</v>
+        <v>-105</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G24">
         <v>823258</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I24">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -2782,67 +3004,67 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2008</v>
+        <v>0.1632</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="P24">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="Q24">
-        <v>0.1887</v>
+        <v>0.114</v>
       </c>
       <c r="R24">
-        <v>0.346</v>
+        <v>0.363</v>
       </c>
       <c r="S24" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T24">
-        <v>0.1935</v>
+        <v>0.19</v>
       </c>
       <c r="U24">
-        <v>0.1889</v>
+        <v>0.1911</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>0.2088</v>
+        <v>0.2167</v>
       </c>
       <c r="X24">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y24">
-        <v>0.9804</v>
+        <v>0.9912</v>
       </c>
       <c r="AA24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.49</v>
+        <v>2.81</v>
       </c>
       <c r="AE24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.1966</v>
+        <v>0.1454</v>
       </c>
       <c r="AG24">
-        <v>0.8748</v>
+        <v>0.8528</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>3.49</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2850,28 +3072,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25">
         <v>3.5</v>
       </c>
       <c r="D25">
-        <v>-147</v>
+        <v>-136</v>
       </c>
       <c r="E25">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
         <v>85</v>
       </c>
       <c r="G25">
-        <v>825043</v>
+        <v>823258</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I25">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2883,67 +3105,67 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.1572</v>
+        <v>0.2008</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="P25">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="Q25">
-        <v>0.1667</v>
+        <v>0.1887</v>
       </c>
       <c r="R25">
-        <v>0.351</v>
+        <v>0.346</v>
       </c>
       <c r="S25" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T25">
-        <v>0.3053</v>
+        <v>0.1935</v>
       </c>
       <c r="U25">
-        <v>0.2844</v>
+        <v>0.1889</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2513</v>
+        <v>0.2088</v>
       </c>
       <c r="X25">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y25">
-        <v>1.0388</v>
+        <v>0.9804</v>
       </c>
       <c r="AA25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.57</v>
+        <v>3.47</v>
       </c>
       <c r="AE25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1605</v>
+        <v>0.1966</v>
       </c>
       <c r="AG25">
-        <v>1.3802</v>
+        <v>0.8688</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.57</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2951,7 +3173,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26">
         <v>3.5</v>
@@ -2963,13 +3185,13 @@
         <v>-132</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G26">
         <v>825043</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26">
         <v>5.4</v>
@@ -3002,7 +3224,7 @@
         <v>0.381</v>
       </c>
       <c r="S26" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="T26">
         <v>0.1637</v>
@@ -3017,34 +3239,34 @@
         <v>0.1752</v>
       </c>
       <c r="X26">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y26">
         <v>0.9178</v>
       </c>
       <c r="AA26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AE26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF26">
         <v>0.1664</v>
       </c>
       <c r="AG26">
-        <v>0.7402</v>
+        <v>0.7351</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3052,19 +3274,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="C27">
+        <v>3.5</v>
+      </c>
+      <c r="D27">
+        <v>-147</v>
+      </c>
+      <c r="E27">
+        <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>823421</v>
+        <v>825043</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I27">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3073,70 +3304,70 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2779</v>
+        <v>0.1572</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="P27">
-        <v>4.16</v>
+        <v>4.34</v>
       </c>
       <c r="Q27">
-        <v>0.2927</v>
+        <v>0.1667</v>
       </c>
       <c r="R27">
-        <v>0.381</v>
+        <v>0.351</v>
       </c>
       <c r="S27" t="s">
+        <v>71</v>
+      </c>
+      <c r="T27">
+        <v>0.3053</v>
+      </c>
+      <c r="U27">
+        <v>0.2844</v>
+      </c>
+      <c r="V27">
+        <v>9</v>
+      </c>
+      <c r="W27">
+        <v>0.2513</v>
+      </c>
+      <c r="X27">
+        <v>0.2227</v>
+      </c>
+      <c r="Y27">
+        <v>1.0388</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD27">
+        <v>4.54</v>
+      </c>
+      <c r="AE27" t="s">
         <v>45</v>
       </c>
-      <c r="T27">
-        <v>0.2015</v>
-      </c>
-      <c r="U27">
-        <v>0.1904</v>
-      </c>
-      <c r="V27">
-        <v>8</v>
-      </c>
-      <c r="W27">
-        <v>0.1857</v>
-      </c>
-      <c r="X27">
-        <v>0.2212</v>
-      </c>
-      <c r="Y27">
-        <v>0.9473</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD27">
-        <v>6.33</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>65</v>
-      </c>
       <c r="AF27">
-        <v>0.2835</v>
+        <v>0.1605</v>
       </c>
       <c r="AG27">
-        <v>0.911</v>
+        <v>1.3707</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>6.33</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3144,19 +3375,28 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="C28">
+        <v>5.5</v>
+      </c>
+      <c r="D28">
+        <v>126</v>
+      </c>
+      <c r="E28">
+        <v>-140</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="G28">
-        <v>823507</v>
+        <v>823745</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3165,70 +3405,70 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2353</v>
+        <v>0.2283</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P28">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="Q28">
-        <v>0.1875</v>
+        <v>0.2719</v>
       </c>
       <c r="R28">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="S28" t="s">
+        <v>71</v>
+      </c>
+      <c r="T28">
+        <v>0.2296</v>
+      </c>
+      <c r="U28">
+        <v>0.2267</v>
+      </c>
+      <c r="V28">
+        <v>8</v>
+      </c>
+      <c r="W28">
+        <v>0.2148</v>
+      </c>
+      <c r="X28">
+        <v>0.2227</v>
+      </c>
+      <c r="Y28">
+        <v>1.0069</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD28">
+        <v>5.71</v>
+      </c>
+      <c r="AE28" t="s">
         <v>45</v>
       </c>
-      <c r="T28">
-        <v>0.2594</v>
-      </c>
-      <c r="U28">
-        <v>0.2717</v>
-      </c>
-      <c r="V28">
-        <v>9</v>
-      </c>
-      <c r="W28">
-        <v>0.2482</v>
-      </c>
-      <c r="X28">
-        <v>0.2212</v>
-      </c>
-      <c r="Y28">
-        <v>1.0239</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD28">
-        <v>6.05</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>65</v>
-      </c>
       <c r="AF28">
-        <v>0.2181</v>
+        <v>0.2442</v>
       </c>
       <c r="AG28">
-        <v>1.1724</v>
+        <v>1.0308</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>6.05</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3236,19 +3476,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>-106</v>
+      </c>
+      <c r="E29">
+        <v>-112</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="G29">
-        <v>823507</v>
+        <v>823745</v>
       </c>
       <c r="H29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3257,70 +3506,70 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>0.2654</v>
+        <v>0.2352</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="P29">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>0.271</v>
+        <v>0.2583</v>
       </c>
       <c r="R29">
-        <v>0.349</v>
+        <v>0.375</v>
       </c>
       <c r="S29" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="T29">
-        <v>0.1935</v>
+        <v>0.2353</v>
       </c>
       <c r="U29">
-        <v>0.1712</v>
+        <v>0.2307</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2104</v>
+        <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2212</v>
+        <v>0.2227</v>
       </c>
       <c r="Y29">
-        <v>0.943</v>
+        <v>1.0121</v>
       </c>
       <c r="AA29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD29">
-        <v>4.65</v>
+        <v>5.76</v>
       </c>
       <c r="AE29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF29">
-        <v>0.2674</v>
+        <v>0.2438</v>
       </c>
       <c r="AG29">
-        <v>0.8746</v>
+        <v>1.0564</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>4.65</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3328,79 +3577,43 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="C30">
+        <v>6.5</v>
+      </c>
+      <c r="D30">
+        <v>-115</v>
+      </c>
+      <c r="E30">
+        <v>-108</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30">
-        <v>824071</v>
+        <v>48</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
-      </c>
-      <c r="I30">
-        <v>4.5</v>
-      </c>
-      <c r="J30" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0.1495</v>
-      </c>
-      <c r="P30">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="S30" t="s">
-        <v>45</v>
-      </c>
-      <c r="T30">
-        <v>0.2083</v>
-      </c>
-      <c r="U30">
-        <v>0.1827</v>
-      </c>
-      <c r="V30">
-        <v>9</v>
-      </c>
-      <c r="W30">
-        <v>0.2078</v>
-      </c>
-      <c r="X30">
-        <v>0.2212</v>
-      </c>
-      <c r="Y30">
-        <v>0.8901</v>
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
       </c>
       <c r="AA30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC30" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD30">
-        <v>2.18</v>
+        <v>44</v>
       </c>
       <c r="AE30" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF30">
-        <v>0.1495</v>
-      </c>
-      <c r="AG30">
-        <v>0.9414</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>2.18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3408,91 +3621,43 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="C31">
+        <v>5.5</v>
+      </c>
+      <c r="D31">
+        <v>110</v>
+      </c>
+      <c r="E31">
+        <v>-125</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31">
-        <v>824150</v>
+        <v>52</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31">
-        <v>2.3</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.19</v>
-      </c>
-      <c r="N31">
-        <v>2</v>
-      </c>
-      <c r="O31">
-        <v>19</v>
-      </c>
-      <c r="P31">
-        <v>4.35</v>
-      </c>
-      <c r="Q31">
-        <v>0.2105</v>
-      </c>
-      <c r="R31">
-        <v>0.087</v>
+        <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>45</v>
-      </c>
-      <c r="T31">
-        <v>0.218</v>
-      </c>
-      <c r="U31">
-        <v>0.2101</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.2091</v>
-      </c>
-      <c r="X31">
-        <v>0.2212</v>
-      </c>
-      <c r="Y31">
-        <v>0.9618</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC31" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD31">
-        <v>1.84</v>
+        <v>44</v>
       </c>
       <c r="AE31" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF31">
-        <v>0.1918</v>
-      </c>
-      <c r="AG31">
-        <v>0.9854</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>1.84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3500,91 +3665,43 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>-133</v>
+      </c>
+      <c r="E32">
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32">
-        <v>824558</v>
+        <v>52</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32">
-        <v>2.1</v>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2261</v>
-      </c>
-      <c r="N32">
-        <v>3</v>
-      </c>
-      <c r="O32">
-        <v>21</v>
-      </c>
-      <c r="P32">
-        <v>4.04</v>
-      </c>
-      <c r="Q32">
-        <v>0.2857</v>
-      </c>
-      <c r="R32">
-        <v>0.095</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>55</v>
-      </c>
-      <c r="T32">
-        <v>0.2104</v>
-      </c>
-      <c r="U32">
-        <v>0.2287</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2302</v>
-      </c>
-      <c r="X32">
-        <v>0.2212</v>
-      </c>
-      <c r="Y32">
-        <v>0.9949</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC32" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD32">
-        <v>1.87</v>
+        <v>44</v>
       </c>
       <c r="AE32" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF32">
-        <v>0.2318</v>
-      </c>
-      <c r="AG32">
-        <v>0.9512</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>1.87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3592,100 +3709,43 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C33">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D33">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E33">
-        <v>-140</v>
+        <v>-162</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
-      </c>
-      <c r="G33">
-        <v>823745</v>
+        <v>55</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
       </c>
       <c r="H33" t="s">
         <v>44</v>
-      </c>
-      <c r="I33">
-        <v>5.4</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
       </c>
       <c r="L33">
         <v>6</v>
       </c>
-      <c r="M33">
-        <v>0.2283</v>
-      </c>
-      <c r="N33">
-        <v>5</v>
-      </c>
-      <c r="O33">
-        <v>114</v>
-      </c>
-      <c r="P33">
-        <v>4.17</v>
-      </c>
-      <c r="Q33">
-        <v>0.2719</v>
-      </c>
-      <c r="R33">
-        <v>0.363</v>
-      </c>
       <c r="S33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T33">
-        <v>0.2296</v>
-      </c>
-      <c r="U33">
-        <v>0.2267</v>
-      </c>
-      <c r="V33">
-        <v>8</v>
-      </c>
-      <c r="W33">
-        <v>0.2148</v>
-      </c>
-      <c r="X33">
-        <v>0.2212</v>
-      </c>
-      <c r="Y33">
-        <v>1.0069</v>
+        <v>44</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
       </c>
       <c r="AA33" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC33" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD33">
-        <v>5.75</v>
+        <v>44</v>
       </c>
       <c r="AE33" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF33">
-        <v>0.2442</v>
-      </c>
-      <c r="AG33">
-        <v>1.038</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>5.75</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3693,100 +3753,43 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C34">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D34">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="E34">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G34">
-        <v>823745</v>
+        <v>77</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
       </c>
       <c r="H34" t="s">
         <v>44</v>
       </c>
-      <c r="I34">
-        <v>5.3</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
       <c r="L34">
-        <v>6</v>
-      </c>
-      <c r="M34">
-        <v>0.2352</v>
-      </c>
-      <c r="N34">
-        <v>5</v>
-      </c>
-      <c r="O34">
-        <v>120</v>
-      </c>
-      <c r="P34">
-        <v>4.2</v>
-      </c>
-      <c r="Q34">
-        <v>0.2583</v>
-      </c>
-      <c r="R34">
-        <v>0.375</v>
+        <v>3</v>
       </c>
       <c r="S34" t="s">
-        <v>55</v>
-      </c>
-      <c r="T34">
-        <v>0.2353</v>
-      </c>
-      <c r="U34">
-        <v>0.2307</v>
-      </c>
-      <c r="V34">
-        <v>9</v>
-      </c>
-      <c r="W34">
-        <v>0.2101</v>
-      </c>
-      <c r="X34">
-        <v>0.2212</v>
-      </c>
-      <c r="Y34">
-        <v>1.0121</v>
+        <v>44</v>
+      </c>
+      <c r="V34" t="s">
+        <v>44</v>
       </c>
       <c r="AA34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC34" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD34">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="AE34" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF34">
-        <v>0.2438</v>
-      </c>
-      <c r="AG34">
-        <v>1.0637</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>5.8</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-23.xlsx
+++ b/data/k-props/2026-08-23.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="97">
   <si>
     <t>date</t>
   </si>
@@ -187,15 +187,12 @@
     <t>Detroit Tigers @ Kansas City Royals</t>
   </si>
   <si>
-    <t>Role unknown</t>
+    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Daniel Lynch IV</t>
   </si>
   <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
     <t>Brady Basso</t>
   </si>
   <si>
@@ -226,67 +223,67 @@
     <t>Los Angeles Angels @ Texas Rangers</t>
   </si>
   <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Blake Snell</t>
+  </si>
+  <si>
+    <t>Shota Imanaga</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Shota Imanaga</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
   </si>
   <si>
     <t>Shane Drohan</t>
@@ -836,7 +833,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -848,22 +845,22 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>0.1446</v>
+        <v>0.1465</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="P2">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="Q2">
-        <v>0.1721</v>
+        <v>0.1667</v>
       </c>
       <c r="R2">
-        <v>0.379</v>
+        <v>0.363</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -881,7 +878,7 @@
         <v>0.2378</v>
       </c>
       <c r="X2">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y2">
         <v>1.0574</v>
@@ -893,22 +890,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.155</v>
+        <v>0.1538</v>
       </c>
       <c r="AG2">
-        <v>1.1569</v>
+        <v>1.1438</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -949,22 +946,22 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>0.2119</v>
+        <v>0.2097</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P3">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="Q3">
-        <v>0.2328</v>
+        <v>0.2389</v>
       </c>
       <c r="R3">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -982,7 +979,7 @@
         <v>0.188</v>
       </c>
       <c r="X3">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -994,22 +991,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2195</v>
+        <v>0.2203</v>
       </c>
       <c r="AG3">
-        <v>0.7578</v>
+        <v>0.7492</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1050,22 +1047,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2151</v>
+        <v>0.2166</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="P4">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="Q4">
-        <v>0.2963</v>
+        <v>0.2727</v>
       </c>
       <c r="R4">
-        <v>0.351</v>
+        <v>0.331</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1083,7 +1080,7 @@
         <v>0.2206</v>
       </c>
       <c r="X4">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y4">
         <v>1.0207</v>
@@ -1095,22 +1092,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.47</v>
+        <v>4.21</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2436</v>
+        <v>0.2352</v>
       </c>
       <c r="AG4">
-        <v>0.8356</v>
+        <v>0.8262</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.47</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1142,22 +1139,22 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.2779</v>
+        <v>0.276</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P5">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="Q5">
-        <v>0.2927</v>
+        <v>0.3009</v>
       </c>
       <c r="R5">
-        <v>0.381</v>
+        <v>0.361</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1175,7 +1172,7 @@
         <v>0.1857</v>
       </c>
       <c r="X5">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y5">
         <v>0.9473</v>
@@ -1187,22 +1184,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="AE5" t="s">
         <v>50</v>
       </c>
       <c r="AF5">
-        <v>0.2835</v>
+        <v>0.285</v>
       </c>
       <c r="AG5">
-        <v>0.9048</v>
+        <v>0.8945</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1222,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1234,22 +1231,22 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.2353</v>
+        <v>0.2348</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="P6">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="Q6">
-        <v>0.1875</v>
+        <v>0.1683</v>
       </c>
       <c r="R6">
-        <v>0.359</v>
+        <v>0.336</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1267,7 +1264,7 @@
         <v>0.2482</v>
       </c>
       <c r="X6">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y6">
         <v>1.0239</v>
@@ -1279,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>6.01</v>
+        <v>5.7</v>
       </c>
       <c r="AE6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2181</v>
+        <v>0.2125</v>
       </c>
       <c r="AG6">
-        <v>1.1644</v>
+        <v>1.1512</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>6.01</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1314,7 +1311,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1326,22 +1323,22 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0.2654</v>
+        <v>0.2544</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="Q7">
-        <v>0.271</v>
+        <v>0.2474</v>
       </c>
       <c r="R7">
-        <v>0.349</v>
+        <v>0.327</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1359,7 +1356,7 @@
         <v>0.2104</v>
       </c>
       <c r="X7">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y7">
         <v>0.943</v>
@@ -1371,22 +1368,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.62</v>
+        <v>4.23</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2674</v>
+        <v>0.2521</v>
       </c>
       <c r="AG7">
-        <v>0.8686</v>
+        <v>0.8588</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.62</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1427,22 +1424,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1667</v>
+        <v>0.1659</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="P8">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="Q8">
-        <v>0.1485</v>
+        <v>0.117</v>
       </c>
       <c r="R8">
-        <v>0.336</v>
+        <v>0.32</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1460,7 +1457,7 @@
         <v>0.2074</v>
       </c>
       <c r="X8">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y8">
         <v>0.9665</v>
@@ -1472,22 +1469,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1606</v>
+        <v>0.1502</v>
       </c>
       <c r="AG8">
-        <v>0.9226</v>
+        <v>0.9122</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1507,7 +1504,7 @@
         <v>58</v>
       </c>
       <c r="I9">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1519,10 +1516,22 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.1495</v>
+        <v>0.1504</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>3.87</v>
+        <v>3.9</v>
+      </c>
+      <c r="Q9">
+        <v>0.1667</v>
+      </c>
+      <c r="R9">
+        <v>0.029</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1540,7 +1549,7 @@
         <v>0.2078</v>
       </c>
       <c r="X9">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y9">
         <v>0.88</v>
@@ -1552,22 +1561,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>2.17</v>
+        <v>0.64</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1495</v>
+        <v>0.1509</v>
       </c>
       <c r="AG9">
-        <v>0.9454</v>
+        <v>0.9347</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>2.17</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1593,10 +1602,10 @@
         <v>824071</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I10">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1608,22 +1617,22 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.1881</v>
+        <v>0.185</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P10">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="Q10">
-        <v>0.1714</v>
+        <v>0.1591</v>
       </c>
       <c r="R10">
-        <v>0.149</v>
+        <v>0.18</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
@@ -1641,7 +1650,7 @@
         <v>0.2286</v>
       </c>
       <c r="X10">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y10">
         <v>0.987</v>
@@ -1653,22 +1662,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1856</v>
+        <v>0.1803</v>
       </c>
       <c r="AG10">
-        <v>0.9072</v>
+        <v>0.897</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1676,19 +1685,19 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
         <v>61</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
       </c>
       <c r="G11">
         <v>824150</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I11">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1700,22 +1709,22 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0.19</v>
+        <v>0.1776</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P11">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="Q11">
-        <v>0.2105</v>
+        <v>0.1538</v>
       </c>
       <c r="R11">
-        <v>0.087</v>
+        <v>0.115</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1733,7 +1742,7 @@
         <v>0.2091</v>
       </c>
       <c r="X11">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y11">
         <v>0.9618</v>
@@ -1745,22 +1754,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1918</v>
+        <v>0.1748</v>
       </c>
       <c r="AG11">
-        <v>0.9786</v>
+        <v>0.9676</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1768,7 +1777,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1780,16 +1789,16 @@
         <v>-115</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>824150</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1801,7 +1810,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.1796</v>
+        <v>0.1965</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1810,10 +1819,10 @@
         <v>88</v>
       </c>
       <c r="P12">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
       <c r="Q12">
-        <v>0.1591</v>
+        <v>0.1932</v>
       </c>
       <c r="R12">
         <v>0.306</v>
@@ -1834,7 +1843,7 @@
         <v>0.212</v>
       </c>
       <c r="X12">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y12">
         <v>1.0766</v>
@@ -1846,22 +1855,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1734</v>
+        <v>0.1955</v>
       </c>
       <c r="AG12">
-        <v>0.9144</v>
+        <v>0.9041</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1869,7 +1878,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>6.5</v>
@@ -1881,7 +1890,7 @@
         <v>-131</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>824558</v>
@@ -1890,7 +1899,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1902,22 +1911,22 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2727</v>
+        <v>0.2757</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="P13">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="Q13">
-        <v>0.216</v>
+        <v>0.219</v>
       </c>
       <c r="R13">
-        <v>0.385</v>
+        <v>0.344</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1935,7 +1944,7 @@
         <v>0.2366</v>
       </c>
       <c r="X13">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y13">
         <v>1.0565</v>
@@ -1947,22 +1956,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AF13">
-        <v>0.2509</v>
+        <v>0.2562</v>
       </c>
       <c r="AG13">
-        <v>1.1295</v>
+        <v>1.1168</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>7.11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1970,16 +1979,16 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>824558</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I14">
         <v>2.1</v>
@@ -1994,22 +2003,22 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.2261</v>
+        <v>0.2302</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="P14">
         <v>4.04</v>
       </c>
       <c r="Q14">
-        <v>0.2857</v>
+        <v>0.3103</v>
       </c>
       <c r="R14">
-        <v>0.095</v>
+        <v>0.127</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
@@ -2027,7 +2036,7 @@
         <v>0.2302</v>
       </c>
       <c r="X14">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y14">
         <v>0.9312</v>
@@ -2039,22 +2048,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2318</v>
+        <v>0.2404</v>
       </c>
       <c r="AG14">
-        <v>0.8059</v>
+        <v>0.7968</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2062,7 +2071,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2074,16 +2083,16 @@
         <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>822856</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I15">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2095,43 +2104,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2324</v>
+        <v>0.2292</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="P15">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="Q15">
-        <v>0.266</v>
+        <v>0.2297</v>
       </c>
       <c r="R15">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="S15" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2342</v>
+        <v>0.2438</v>
       </c>
       <c r="U15">
-        <v>0.2346</v>
+        <v>0.2391</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>0.2443</v>
       </c>
       <c r="X15">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y15">
-        <v>1.0256</v>
+        <v>1.0672</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2140,22 +2149,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.32</v>
+        <v>4.77</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2431</v>
+        <v>0.2293</v>
       </c>
       <c r="AG15">
-        <v>1.0513</v>
+        <v>1.0823</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.32</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2163,7 +2172,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2175,7 +2184,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>822856</v>
@@ -2184,7 +2193,7 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2196,22 +2205,22 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0.1672</v>
+        <v>0.1682</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="P16">
         <v>4.16</v>
       </c>
       <c r="Q16">
-        <v>0.2212</v>
+        <v>0.2447</v>
       </c>
       <c r="R16">
-        <v>0.361</v>
+        <v>0.32</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
@@ -2229,7 +2238,7 @@
         <v>0.2508</v>
       </c>
       <c r="X16">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y16">
         <v>1.0756</v>
@@ -2241,22 +2250,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.45</v>
+        <v>5.12</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1867</v>
+        <v>0.1927</v>
       </c>
       <c r="AG16">
-        <v>1.3256</v>
+        <v>1.3107</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.45</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2264,7 +2273,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2276,7 +2285,7 @@
         <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G17">
         <v>824315</v>
@@ -2315,25 +2324,25 @@
         <v>0.367</v>
       </c>
       <c r="S17" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2277</v>
+        <v>0.2477</v>
       </c>
       <c r="U17">
-        <v>0.2227</v>
+        <v>0.2355</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>0.249</v>
       </c>
       <c r="X17">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y17">
-        <v>1.0052</v>
+        <v>1.0231</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2342,7 +2351,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.94</v>
+        <v>5.41</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2351,13 +2360,13 @@
         <v>0.2041</v>
       </c>
       <c r="AG17">
-        <v>1.0222</v>
+        <v>1.0996</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.94</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2365,7 +2374,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>2.5</v>
@@ -2377,7 +2386,7 @@
         <v>-110</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G18">
         <v>824315</v>
@@ -2431,7 +2440,7 @@
         <v>0.2125</v>
       </c>
       <c r="X18">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y18">
         <v>0.88</v>
@@ -2443,7 +2452,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2452,13 +2461,13 @@
         <v>0.1447</v>
       </c>
       <c r="AG18">
-        <v>0.8285</v>
+        <v>0.8192</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2466,7 +2475,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2478,7 +2487,7 @@
         <v>112</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>824720</v>
@@ -2532,7 +2541,7 @@
         <v>0.2355</v>
       </c>
       <c r="X19">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y19">
         <v>1.0136</v>
@@ -2544,7 +2553,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.28</v>
+        <v>5.22</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2553,13 +2562,13 @@
         <v>0.1899</v>
       </c>
       <c r="AG19">
-        <v>1.1898</v>
+        <v>1.1763</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.28</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2567,7 +2576,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>2.5</v>
@@ -2579,13 +2588,13 @@
         <v>-179</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G20">
         <v>823909</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I20">
         <v>2.4</v>
@@ -2618,13 +2627,13 @@
         <v>0.19</v>
       </c>
       <c r="S20" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.3057</v>
+        <v>0.2365</v>
       </c>
       <c r="U20">
-        <v>0.2029</v>
+        <v>0.2065</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2633,10 +2642,10 @@
         <v>0.2075</v>
       </c>
       <c r="X20">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y20">
-        <v>1.0048</v>
+        <v>0.9976</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2645,7 +2654,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>3.64</v>
+        <v>2.76</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2654,13 +2663,13 @@
         <v>0.2667</v>
       </c>
       <c r="AG20">
-        <v>1.3726</v>
+        <v>1.0497</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>3.64</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2668,7 +2677,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>8.5</v>
@@ -2680,7 +2689,7 @@
         <v>-110</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G21">
         <v>823909</v>
@@ -2719,13 +2728,13 @@
         <v>0.24</v>
       </c>
       <c r="S21" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.1949</v>
+        <v>0.2683</v>
       </c>
       <c r="U21">
-        <v>0.2198</v>
+        <v>0.2606</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2734,10 +2743,10 @@
         <v>0.2592</v>
       </c>
       <c r="X21">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y21">
-        <v>1.0078</v>
+        <v>1.0405</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2746,22 +2755,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.88</v>
+        <v>8.26</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AF21">
         <v>0.3175</v>
       </c>
       <c r="AG21">
-        <v>0.8751</v>
+        <v>1.1909</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.88</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2769,7 +2778,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2781,7 +2790,7 @@
         <v>-106</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>823099</v>
@@ -2820,13 +2829,13 @@
         <v>0.363</v>
       </c>
       <c r="S22" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2425</v>
+        <v>0.2043</v>
       </c>
       <c r="U22">
-        <v>0.216</v>
+        <v>0.2108</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2835,10 +2844,10 @@
         <v>0.2418</v>
       </c>
       <c r="X22">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y22">
-        <v>0.991</v>
+        <v>0.972</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2847,22 +2856,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>6.31</v>
+        <v>5.16</v>
       </c>
       <c r="AE22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF22">
         <v>0.253</v>
       </c>
       <c r="AG22">
-        <v>1.0885</v>
+        <v>0.907</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>6.31</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2870,7 +2879,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2882,7 +2891,7 @@
         <v>-165</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>823099</v>
@@ -2921,13 +2930,13 @@
         <v>0.361</v>
       </c>
       <c r="S23" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2285</v>
+        <v>0.2255</v>
       </c>
       <c r="U23">
-        <v>0.2264</v>
+        <v>0.2241</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2936,10 +2945,10 @@
         <v>0.2194</v>
       </c>
       <c r="X23">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y23">
-        <v>0.9775</v>
+        <v>0.941</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2948,7 +2957,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2957,13 +2966,13 @@
         <v>0.2089</v>
       </c>
       <c r="AG23">
-        <v>1.0258</v>
+        <v>1.0009</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2971,7 +2980,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -2983,7 +2992,7 @@
         <v>-105</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G24">
         <v>823258</v>
@@ -3022,25 +3031,25 @@
         <v>0.363</v>
       </c>
       <c r="S24" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T24">
+        <v>0.1883</v>
+      </c>
+      <c r="U24">
         <v>0.19</v>
       </c>
-      <c r="U24">
-        <v>0.1911</v>
-      </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>0.2167</v>
       </c>
       <c r="X24">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y24">
-        <v>0.9912</v>
+        <v>0.9918</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3049,7 +3058,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3058,13 +3067,13 @@
         <v>0.1454</v>
       </c>
       <c r="AG24">
-        <v>0.8528</v>
+        <v>0.8356</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3072,7 +3081,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>3.5</v>
@@ -3084,7 +3093,7 @@
         <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G25">
         <v>823258</v>
@@ -3123,13 +3132,13 @@
         <v>0.346</v>
       </c>
       <c r="S25" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.1935</v>
+        <v>0.2006</v>
       </c>
       <c r="U25">
-        <v>0.1889</v>
+        <v>0.1925</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -3138,10 +3147,10 @@
         <v>0.2088</v>
       </c>
       <c r="X25">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y25">
-        <v>0.9804</v>
+        <v>0.9654</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3150,7 +3159,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
@@ -3159,13 +3168,13 @@
         <v>0.1966</v>
       </c>
       <c r="AG25">
-        <v>0.8688</v>
+        <v>0.8902</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3173,7 +3182,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>3.5</v>
@@ -3185,7 +3194,7 @@
         <v>-132</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G26">
         <v>825043</v>
@@ -3224,13 +3233,13 @@
         <v>0.381</v>
       </c>
       <c r="S26" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.1637</v>
+        <v>0.1905</v>
       </c>
       <c r="U26">
-        <v>0.1649</v>
+        <v>0.1691</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -3239,10 +3248,10 @@
         <v>0.1752</v>
       </c>
       <c r="X26">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y26">
-        <v>0.9178</v>
+        <v>0.88</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3251,7 +3260,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3260,13 +3269,13 @@
         <v>0.1664</v>
       </c>
       <c r="AG26">
-        <v>0.7351</v>
+        <v>0.8454</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3274,7 +3283,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3286,7 +3295,7 @@
         <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>825043</v>
@@ -3325,13 +3334,13 @@
         <v>0.351</v>
       </c>
       <c r="S27" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.3053</v>
+        <v>0.3569</v>
       </c>
       <c r="U27">
-        <v>0.2844</v>
+        <v>0.281</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -3340,10 +3349,10 @@
         <v>0.2513</v>
       </c>
       <c r="X27">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y27">
-        <v>1.0388</v>
+        <v>1.0765</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3352,7 +3361,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.54</v>
+        <v>5.44</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
@@ -3361,13 +3370,13 @@
         <v>0.1605</v>
       </c>
       <c r="AG27">
-        <v>1.3707</v>
+        <v>1.5842</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>4.54</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3375,7 +3384,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3387,7 +3396,7 @@
         <v>-140</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G28">
         <v>823745</v>
@@ -3426,7 +3435,7 @@
         <v>0.363</v>
       </c>
       <c r="S28" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="T28">
         <v>0.2296</v>
@@ -3441,7 +3450,7 @@
         <v>0.2148</v>
       </c>
       <c r="X28">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y28">
         <v>1.0069</v>
@@ -3453,7 +3462,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.71</v>
+        <v>5.64</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3462,13 +3471,13 @@
         <v>0.2442</v>
       </c>
       <c r="AG28">
-        <v>1.0308</v>
+        <v>1.0192</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.71</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3476,7 +3485,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3488,7 +3497,7 @@
         <v>-112</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G29">
         <v>823745</v>
@@ -3527,7 +3536,7 @@
         <v>0.375</v>
       </c>
       <c r="S29" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="T29">
         <v>0.2353</v>
@@ -3542,7 +3551,7 @@
         <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2227</v>
+        <v>0.2253</v>
       </c>
       <c r="Y29">
         <v>1.0121</v>
@@ -3554,7 +3563,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.76</v>
+        <v>5.69</v>
       </c>
       <c r="AE29" t="s">
         <v>45</v>
@@ -3563,13 +3572,13 @@
         <v>0.2438</v>
       </c>
       <c r="AG29">
-        <v>1.0564</v>
+        <v>1.0445</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>5.76</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3577,7 +3586,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C30">
         <v>6.5</v>
@@ -3621,7 +3630,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -3665,7 +3674,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32">
         <v>4.5</v>
@@ -3709,7 +3718,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -3753,7 +3762,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C34">
         <v>2.5</v>
@@ -3765,7 +3774,7 @@
         <v>-110</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-23.xlsx
+++ b/data/k-props/2026-08-23.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -211,45 +211,45 @@
     <t>New York Mets @ Chicago White Sox</t>
   </si>
   <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Yusei Kikuchi</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Blake Snell</t>
+  </si>
+  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Sean Newcomb</t>
-  </si>
-  <si>
-    <t>Yusei Kikuchi</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Blake Snell</t>
-  </si>
-  <si>
     <t>Shota Imanaga</t>
   </si>
   <si>
@@ -281,9 +281,6 @@
   </si>
   <si>
     <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>Shane Drohan</t>
@@ -833,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -845,22 +842,22 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>0.1465</v>
+        <v>0.1467</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="P2">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="Q2">
         <v>0.1667</v>
       </c>
       <c r="R2">
-        <v>0.363</v>
+        <v>0.375</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -875,10 +872,10 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2378</v>
+        <v>0.2374</v>
       </c>
       <c r="X2">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y2">
         <v>1.0574</v>
@@ -890,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1538</v>
+        <v>0.1542</v>
       </c>
       <c r="AG2">
-        <v>1.1438</v>
+        <v>1.1418</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -946,22 +943,22 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>0.2097</v>
+        <v>0.2093</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="P3">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="Q3">
-        <v>0.2389</v>
+        <v>0.2353</v>
       </c>
       <c r="R3">
-        <v>0.361</v>
+        <v>0.373</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -976,10 +973,10 @@
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.188</v>
+        <v>0.1872</v>
       </c>
       <c r="X3">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y3">
         <v>0.88</v>
@@ -991,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2203</v>
+        <v>0.219</v>
       </c>
       <c r="AG3">
-        <v>0.7492</v>
+        <v>0.7479</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1077,10 +1074,10 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2206</v>
+        <v>0.2199</v>
       </c>
       <c r="X4">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y4">
         <v>1.0207</v>
@@ -1092,7 +1089,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1101,13 +1098,13 @@
         <v>0.2352</v>
       </c>
       <c r="AG4">
-        <v>0.8262</v>
+        <v>0.8247</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1139,22 +1136,22 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.276</v>
+        <v>0.2767</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="P5">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="Q5">
-        <v>0.3009</v>
+        <v>0.3008</v>
       </c>
       <c r="R5">
-        <v>0.361</v>
+        <v>0.381</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1169,10 +1166,10 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>0.1857</v>
+        <v>0.1868</v>
       </c>
       <c r="X5">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y5">
         <v>0.9473</v>
@@ -1184,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.19</v>
+        <v>6.28</v>
       </c>
       <c r="AE5" t="s">
         <v>50</v>
       </c>
       <c r="AF5">
-        <v>0.285</v>
+        <v>0.2859</v>
       </c>
       <c r="AG5">
-        <v>0.8945</v>
+        <v>0.8929</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.19</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1219,7 +1216,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1231,22 +1228,22 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0.2348</v>
+        <v>0.2371</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="P6">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="Q6">
-        <v>0.1683</v>
+        <v>0.1875</v>
       </c>
       <c r="R6">
-        <v>0.336</v>
+        <v>0.359</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1261,10 +1258,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2482</v>
+        <v>0.2485</v>
       </c>
       <c r="X6">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y6">
         <v>1.0239</v>
@@ -1276,22 +1273,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.7</v>
+        <v>5.99</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2125</v>
+        <v>0.2193</v>
       </c>
       <c r="AG6">
-        <v>1.1512</v>
+        <v>1.1492</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>5.7</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1329,16 +1326,16 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P7">
         <v>4.2</v>
       </c>
       <c r="Q7">
-        <v>0.2474</v>
+        <v>0.2424</v>
       </c>
       <c r="R7">
-        <v>0.327</v>
+        <v>0.331</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1353,10 +1350,10 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2104</v>
+        <v>0.2097</v>
       </c>
       <c r="X7">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y7">
         <v>0.943</v>
@@ -1368,22 +1365,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2521</v>
+        <v>0.2504</v>
       </c>
       <c r="AG7">
-        <v>0.8588</v>
+        <v>0.8572</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1424,22 +1421,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1659</v>
+        <v>0.1643</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="P8">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="Q8">
-        <v>0.117</v>
+        <v>0.1122</v>
       </c>
       <c r="R8">
-        <v>0.32</v>
+        <v>0.329</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1454,10 +1451,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2074</v>
+        <v>0.2071</v>
       </c>
       <c r="X8">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y8">
         <v>0.9665</v>
@@ -1469,22 +1466,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1502</v>
+        <v>0.1471</v>
       </c>
       <c r="AG8">
-        <v>0.9122</v>
+        <v>0.9106</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1546,10 +1543,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2078</v>
+        <v>0.208</v>
       </c>
       <c r="X9">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y9">
         <v>0.88</v>
@@ -1570,7 +1567,7 @@
         <v>0.1509</v>
       </c>
       <c r="AG9">
-        <v>0.9347</v>
+        <v>0.933</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1605,7 +1602,7 @@
         <v>58</v>
       </c>
       <c r="I10">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1617,22 +1614,22 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.185</v>
+        <v>0.183</v>
       </c>
       <c r="N10">
         <v>4</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="P10">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="Q10">
-        <v>0.1591</v>
+        <v>0.1538</v>
       </c>
       <c r="R10">
-        <v>0.18</v>
+        <v>0.206</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
@@ -1647,10 +1644,10 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2286</v>
+        <v>0.2268</v>
       </c>
       <c r="X10">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y10">
         <v>0.987</v>
@@ -1662,22 +1659,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1803</v>
+        <v>0.177</v>
       </c>
       <c r="AG10">
-        <v>0.897</v>
+        <v>0.8954</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1739,10 +1736,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2091</v>
+        <v>0.209</v>
       </c>
       <c r="X11">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y11">
         <v>0.9618</v>
@@ -1763,7 +1760,7 @@
         <v>0.1748</v>
       </c>
       <c r="AG11">
-        <v>0.9676</v>
+        <v>0.9658</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1798,7 +1795,7 @@
         <v>63</v>
       </c>
       <c r="I12">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1810,22 +1807,22 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.1965</v>
+        <v>0.2054</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="Q12">
-        <v>0.1932</v>
+        <v>0.21</v>
       </c>
       <c r="R12">
-        <v>0.306</v>
+        <v>0.333</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
@@ -1840,10 +1837,10 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.212</v>
+        <v>0.2138</v>
       </c>
       <c r="X12">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y12">
         <v>1.0766</v>
@@ -1855,22 +1852,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1955</v>
+        <v>0.2069</v>
       </c>
       <c r="AG12">
-        <v>0.9041</v>
+        <v>0.9024</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1899,7 +1896,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1911,22 +1908,22 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2757</v>
+        <v>0.2718</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="P13">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="Q13">
-        <v>0.219</v>
+        <v>0.2131</v>
       </c>
       <c r="R13">
-        <v>0.344</v>
+        <v>0.379</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1941,10 +1938,10 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2366</v>
+        <v>0.2371</v>
       </c>
       <c r="X13">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y13">
         <v>1.0565</v>
@@ -1956,22 +1953,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="AE13" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AF13">
-        <v>0.2562</v>
+        <v>0.2496</v>
       </c>
       <c r="AG13">
-        <v>1.1168</v>
+        <v>1.1147</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>7</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1979,7 +1976,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
@@ -2033,10 +2030,10 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2302</v>
+        <v>0.2322</v>
       </c>
       <c r="X14">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y14">
         <v>0.9312</v>
@@ -2057,7 +2054,7 @@
         <v>0.2404</v>
       </c>
       <c r="AG14">
-        <v>0.7968</v>
+        <v>0.7954</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -2071,7 +2068,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2083,16 +2080,16 @@
         <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>822856</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2104,22 +2101,22 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2292</v>
+        <v>0.2242</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="P15">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="Q15">
-        <v>0.2297</v>
+        <v>0.2211</v>
       </c>
       <c r="R15">
-        <v>0.27</v>
+        <v>0.322</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
@@ -2134,10 +2131,10 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2443</v>
+        <v>0.243</v>
       </c>
       <c r="X15">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y15">
         <v>1.0672</v>
@@ -2149,22 +2146,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.77</v>
+        <v>5.31</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2293</v>
+        <v>0.2232</v>
       </c>
       <c r="AG15">
-        <v>1.0823</v>
+        <v>1.0803</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.77</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2172,7 +2169,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2184,7 +2181,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>822856</v>
@@ -2193,7 +2190,7 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2205,22 +2202,22 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0.1682</v>
+        <v>0.1729</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="P16">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="Q16">
-        <v>0.2447</v>
+        <v>0.2456</v>
       </c>
       <c r="R16">
-        <v>0.32</v>
+        <v>0.363</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
@@ -2235,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2508</v>
+        <v>0.2509</v>
       </c>
       <c r="X16">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y16">
         <v>1.0756</v>
@@ -2250,22 +2247,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.12</v>
+        <v>5.84</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
       </c>
       <c r="AF16">
-        <v>0.1927</v>
+        <v>0.1988</v>
       </c>
       <c r="AG16">
-        <v>1.3107</v>
+        <v>1.3083</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.12</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2273,7 +2270,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2285,7 +2282,7 @@
         <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17">
         <v>824315</v>
@@ -2294,7 +2291,7 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2306,22 +2303,22 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2224</v>
+        <v>0.2209</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="P17">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="Q17">
-        <v>0.1724</v>
+        <v>0.1964</v>
       </c>
       <c r="R17">
-        <v>0.367</v>
+        <v>0.359</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
@@ -2339,7 +2336,7 @@
         <v>0.249</v>
       </c>
       <c r="X17">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y17">
         <v>1.0231</v>
@@ -2351,22 +2348,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.41</v>
+        <v>5.6</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2041</v>
+        <v>0.2121</v>
       </c>
       <c r="AG17">
-        <v>1.0996</v>
+        <v>1.0976</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>5.41</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2374,7 +2371,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>2.5</v>
@@ -2386,7 +2383,7 @@
         <v>-110</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G18">
         <v>824315</v>
@@ -2395,7 +2392,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2407,22 +2404,22 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1386</v>
+        <v>0.1376</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="Q18">
-        <v>0.1552</v>
+        <v>0.1351</v>
       </c>
       <c r="R18">
-        <v>0.367</v>
+        <v>0.357</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
@@ -2440,7 +2437,7 @@
         <v>0.2125</v>
       </c>
       <c r="X18">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y18">
         <v>0.88</v>
@@ -2452,22 +2449,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.1447</v>
+        <v>0.1367</v>
       </c>
       <c r="AG18">
-        <v>0.8192</v>
+        <v>0.8177</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2475,7 +2472,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2487,7 +2484,7 @@
         <v>112</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19">
         <v>824720</v>
@@ -2508,22 +2505,22 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.1889</v>
+        <v>0.1903</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="Q19">
-        <v>0.1917</v>
+        <v>0.2033</v>
       </c>
       <c r="R19">
-        <v>0.375</v>
+        <v>0.381</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
@@ -2541,7 +2538,7 @@
         <v>0.2355</v>
       </c>
       <c r="X19">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y19">
         <v>1.0136</v>
@@ -2553,22 +2550,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.22</v>
+        <v>5.45</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1899</v>
+        <v>0.1953</v>
       </c>
       <c r="AG19">
-        <v>1.1763</v>
+        <v>1.1742</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.22</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2576,7 +2573,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>2.5</v>
@@ -2588,7 +2585,7 @@
         <v>-179</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G20">
         <v>823909</v>
@@ -2597,7 +2594,7 @@
         <v>58</v>
       </c>
       <c r="I20">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -2609,7 +2606,7 @@
         <v>2</v>
       </c>
       <c r="M20">
-        <v>0.2544</v>
+        <v>0.25</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -2618,10 +2615,10 @@
         <v>47</v>
       </c>
       <c r="P20">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="Q20">
-        <v>0.3191</v>
+        <v>0.2766</v>
       </c>
       <c r="R20">
         <v>0.19</v>
@@ -2642,7 +2639,7 @@
         <v>0.2075</v>
       </c>
       <c r="X20">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y20">
         <v>0.9976</v>
@@ -2654,22 +2651,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2667</v>
+        <v>0.2551</v>
       </c>
       <c r="AG20">
-        <v>1.0497</v>
+        <v>1.0478</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2677,7 +2674,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21">
         <v>8.5</v>
@@ -2689,7 +2686,7 @@
         <v>-110</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>823909</v>
@@ -2698,7 +2695,7 @@
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2710,22 +2707,22 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.3175</v>
+        <v>0.2892</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="P21">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="Q21">
-        <v>0.3175</v>
+        <v>0.2927</v>
       </c>
       <c r="R21">
-        <v>0.24</v>
+        <v>0.291</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
@@ -2743,7 +2740,7 @@
         <v>0.2592</v>
       </c>
       <c r="X21">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y21">
         <v>1.0405</v>
@@ -2755,22 +2752,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>8.26</v>
+        <v>7.45</v>
       </c>
       <c r="AE21" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="AF21">
-        <v>0.3175</v>
+        <v>0.2902</v>
       </c>
       <c r="AG21">
-        <v>1.1909</v>
+        <v>1.1888</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>8.26</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2799,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2811,22 +2808,22 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2422</v>
+        <v>0.2432</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="P22">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="Q22">
-        <v>0.2719</v>
+        <v>0.2952</v>
       </c>
       <c r="R22">
-        <v>0.363</v>
+        <v>0.344</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
@@ -2844,7 +2841,7 @@
         <v>0.2418</v>
       </c>
       <c r="X22">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y22">
         <v>0.972</v>
@@ -2856,22 +2853,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.253</v>
+        <v>0.2611</v>
       </c>
       <c r="AG22">
-        <v>0.907</v>
+        <v>0.9054</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2900,7 +2897,7 @@
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2912,22 +2909,22 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2458</v>
+        <v>0.248</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="P23">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="Q23">
-        <v>0.1416</v>
+        <v>0.2</v>
       </c>
       <c r="R23">
-        <v>0.361</v>
+        <v>0.344</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
@@ -2945,7 +2942,7 @@
         <v>0.2194</v>
       </c>
       <c r="X23">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y23">
         <v>0.941</v>
@@ -2957,22 +2954,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.38</v>
+        <v>4.74</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.2089</v>
+        <v>0.2315</v>
       </c>
       <c r="AG23">
-        <v>1.0009</v>
+        <v>0.9991</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.38</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3013,22 +3010,22 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.1632</v>
+        <v>0.1619</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P24">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="Q24">
-        <v>0.114</v>
+        <v>0.1217</v>
       </c>
       <c r="R24">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
@@ -3046,7 +3043,7 @@
         <v>0.2167</v>
       </c>
       <c r="X24">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y24">
         <v>0.9918</v>
@@ -3058,22 +3055,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.1454</v>
+        <v>0.1473</v>
       </c>
       <c r="AG24">
-        <v>0.8356</v>
+        <v>0.8341</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3114,22 +3111,22 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2008</v>
+        <v>0.1981</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="P25">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="Q25">
-        <v>0.1887</v>
+        <v>0.1485</v>
       </c>
       <c r="R25">
-        <v>0.346</v>
+        <v>0.336</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
@@ -3147,7 +3144,7 @@
         <v>0.2088</v>
       </c>
       <c r="X25">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y25">
         <v>0.9654</v>
@@ -3159,22 +3156,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1966</v>
+        <v>0.1815</v>
       </c>
       <c r="AG25">
-        <v>0.8902</v>
+        <v>0.8886</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3203,7 +3200,7 @@
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3215,22 +3212,22 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1788</v>
+        <v>0.1796</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="P26">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="Q26">
-        <v>0.1463</v>
+        <v>0.1532</v>
       </c>
       <c r="R26">
-        <v>0.381</v>
+        <v>0.357</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
@@ -3248,7 +3245,7 @@
         <v>0.1752</v>
       </c>
       <c r="X26">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y26">
         <v>0.88</v>
@@ -3260,22 +3257,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.1664</v>
+        <v>0.1702</v>
       </c>
       <c r="AG26">
-        <v>0.8454</v>
+        <v>0.8439</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3301,10 +3298,10 @@
         <v>825043</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="I27">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3316,22 +3313,22 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1572</v>
+        <v>0.1591</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="P27">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
       <c r="Q27">
-        <v>0.1667</v>
+        <v>0.1818</v>
       </c>
       <c r="R27">
-        <v>0.351</v>
+        <v>0.331</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
@@ -3349,7 +3346,7 @@
         <v>0.2513</v>
       </c>
       <c r="X27">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y27">
         <v>1.0765</v>
@@ -3361,22 +3358,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>5.44</v>
+        <v>5.55</v>
       </c>
       <c r="AE27" t="s">
         <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.1605</v>
+        <v>0.1666</v>
       </c>
       <c r="AG27">
-        <v>1.5842</v>
+        <v>1.5814</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>5.44</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3435,25 +3432,25 @@
         <v>0.363</v>
       </c>
       <c r="S28" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2296</v>
+        <v>0.2279</v>
       </c>
       <c r="U28">
-        <v>0.2267</v>
+        <v>0.2255</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>0.2148</v>
       </c>
       <c r="X28">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y28">
-        <v>1.0069</v>
+        <v>1.04</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3462,7 +3459,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.64</v>
+        <v>5.78</v>
       </c>
       <c r="AE28" t="s">
         <v>45</v>
@@ -3471,13 +3468,13 @@
         <v>0.2442</v>
       </c>
       <c r="AG28">
-        <v>1.0192</v>
+        <v>1.0098</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.64</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3485,7 +3482,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3536,13 +3533,13 @@
         <v>0.375</v>
       </c>
       <c r="S29" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2353</v>
+        <v>0.2492</v>
       </c>
       <c r="U29">
-        <v>0.2307</v>
+        <v>0.2333</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3551,10 +3548,10 @@
         <v>0.2101</v>
       </c>
       <c r="X29">
-        <v>0.2253</v>
+        <v>0.2257</v>
       </c>
       <c r="Y29">
-        <v>1.0121</v>
+        <v>1.0258</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3563,22 +3560,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.69</v>
+        <v>6.1</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF29">
         <v>0.2438</v>
       </c>
       <c r="AG29">
-        <v>1.0445</v>
+        <v>1.1041</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>5.69</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3586,7 +3583,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30">
         <v>6.5</v>
@@ -3630,7 +3627,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -3674,7 +3671,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>4.5</v>
@@ -3718,7 +3715,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -3762,7 +3759,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34">
         <v>2.5</v>
@@ -3774,7 +3771,7 @@
         <v>-110</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-23.xlsx
+++ b/data/k-props/2026-08-23.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="100">
   <si>
     <t>date</t>
   </si>
@@ -145,24 +145,33 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
@@ -203,6 +212,9 @@
   </si>
   <si>
     <t>Limited starter</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Nolan McLean</t>
@@ -880,17 +892,23 @@
       <c r="Y2">
         <v>1.0574</v>
       </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>0.92</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>4.42</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.1542</v>
@@ -900,6 +918,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>-0.42</v>
+      </c>
+      <c r="AJ2">
+        <v>0.42</v>
+      </c>
+      <c r="AK2">
+        <v>-0.42</v>
+      </c>
+      <c r="AL2">
+        <v>0.42</v>
       </c>
       <c r="AM2">
         <v>4.42</v>
@@ -910,7 +940,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -981,17 +1011,23 @@
       <c r="Y3">
         <v>0.88</v>
       </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>-0.92</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3">
         <v>3.58</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.219</v>
@@ -1001,6 +1037,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-0.58</v>
+      </c>
+      <c r="AJ3">
+        <v>0.58</v>
+      </c>
+      <c r="AK3">
+        <v>-0.58</v>
+      </c>
+      <c r="AL3">
+        <v>0.58</v>
       </c>
       <c r="AM3">
         <v>3.58</v>
@@ -1011,7 +1059,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -1023,7 +1071,7 @@
         <v>132</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>823421</v>
@@ -1082,17 +1130,23 @@
       <c r="Y4">
         <v>1.0207</v>
       </c>
+      <c r="Z4">
+        <v>4</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>0.7</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD4">
         <v>4.2</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.2352</v>
@@ -1102,6 +1156,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>-0.2</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2</v>
+      </c>
+      <c r="AL4">
+        <v>0.2</v>
       </c>
       <c r="AM4">
         <v>4.2</v>
@@ -1112,10 +1178,10 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>823421</v>
@@ -1175,16 +1241,16 @@
         <v>0.9473</v>
       </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD5">
         <v>6.28</v>
       </c>
       <c r="AE5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AF5">
         <v>0.2859</v>
@@ -1204,10 +1270,10 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>823507</v>
@@ -1267,16 +1333,16 @@
         <v>1.0239</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD6">
         <v>5.99</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.2193</v>
@@ -1296,10 +1362,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>823507</v>
@@ -1359,16 +1425,16 @@
         <v>0.943</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD7">
         <v>4.2</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.2504</v>
@@ -1388,7 +1454,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1400,7 +1466,7 @@
         <v>-115</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>823827</v>
@@ -1459,17 +1525,23 @@
       <c r="Y8">
         <v>0.9665</v>
       </c>
+      <c r="Z8">
+        <v>2</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB8">
+        <v>-0.68</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD8">
         <v>2.82</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.1471</v>
@@ -1479,6 +1551,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-0.82</v>
+      </c>
+      <c r="AJ8">
+        <v>0.82</v>
+      </c>
+      <c r="AK8">
+        <v>-0.82</v>
+      </c>
+      <c r="AL8">
+        <v>0.82</v>
       </c>
       <c r="AM8">
         <v>2.82</v>
@@ -1489,16 +1573,16 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>824071</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I9">
         <v>1.3</v>
@@ -1552,16 +1636,16 @@
         <v>0.88</v>
       </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD9">
         <v>0.64</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.1509</v>
@@ -1581,7 +1665,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2.5</v>
@@ -1593,13 +1677,13 @@
         <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>824071</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I10">
         <v>3</v>
@@ -1652,17 +1736,23 @@
       <c r="Y10">
         <v>0.987</v>
       </c>
+      <c r="Z10">
+        <v>2</v>
+      </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB10">
+        <v>-0.61</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD10">
         <v>1.89</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.177</v>
@@ -1672,6 +1762,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0.11</v>
+      </c>
+      <c r="AJ10">
+        <v>0.11</v>
+      </c>
+      <c r="AK10">
+        <v>0.11</v>
+      </c>
+      <c r="AL10">
+        <v>0.11</v>
       </c>
       <c r="AM10">
         <v>1.89</v>
@@ -1682,16 +1784,16 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>824150</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I11">
         <v>1.9</v>
@@ -1745,16 +1847,16 @@
         <v>0.9618</v>
       </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD11">
         <v>1.37</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.1748</v>
@@ -1774,7 +1876,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1786,13 +1888,13 @@
         <v>-115</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>824150</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I12">
         <v>3.9</v>
@@ -1845,17 +1947,23 @@
       <c r="Y12">
         <v>1.0766</v>
       </c>
+      <c r="Z12">
+        <v>8</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>-0.89</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AD12">
         <v>3.61</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.2069</v>
@@ -1865,6 +1973,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>4.39</v>
+      </c>
+      <c r="AJ12">
+        <v>4.39</v>
+      </c>
+      <c r="AK12">
+        <v>4.39</v>
+      </c>
+      <c r="AL12">
+        <v>4.39</v>
       </c>
       <c r="AM12">
         <v>3.61</v>
@@ -1875,7 +1995,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>6.5</v>
@@ -1887,7 +2007,7 @@
         <v>-131</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>824558</v>
@@ -1946,17 +2066,23 @@
       <c r="Y13">
         <v>1.0565</v>
       </c>
+      <c r="Z13">
+        <v>6</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB13">
+        <v>0.49</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD13">
         <v>6.99</v>
       </c>
       <c r="AE13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AF13">
         <v>0.2496</v>
@@ -1966,6 +2092,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>-0.99</v>
+      </c>
+      <c r="AJ13">
+        <v>0.99</v>
+      </c>
+      <c r="AK13">
+        <v>-0.99</v>
+      </c>
+      <c r="AL13">
+        <v>0.99</v>
       </c>
       <c r="AM13">
         <v>6.99</v>
@@ -1976,16 +2114,16 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>824558</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I14">
         <v>2.1</v>
@@ -2039,16 +2177,16 @@
         <v>0.9312</v>
       </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD14">
         <v>1.5</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.2404</v>
@@ -2068,7 +2206,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2080,7 +2218,7 @@
         <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G15">
         <v>822856</v>
@@ -2139,17 +2277,23 @@
       <c r="Y15">
         <v>1.0672</v>
       </c>
+      <c r="Z15">
+        <v>4</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB15">
+        <v>0.81</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AD15">
         <v>5.31</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.2232</v>
@@ -2159,6 +2303,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>-1.31</v>
+      </c>
+      <c r="AJ15">
+        <v>1.31</v>
+      </c>
+      <c r="AK15">
+        <v>-1.31</v>
+      </c>
+      <c r="AL15">
+        <v>1.31</v>
       </c>
       <c r="AM15">
         <v>5.31</v>
@@ -2169,7 +2325,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2181,7 +2337,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>822856</v>
@@ -2240,17 +2396,23 @@
       <c r="Y16">
         <v>1.0756</v>
       </c>
+      <c r="Z16">
+        <v>6</v>
+      </c>
       <c r="AA16" t="s">
         <v>44</v>
       </c>
+      <c r="AB16">
+        <v>2.34</v>
+      </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD16">
         <v>5.84</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1988</v>
@@ -2260,6 +2422,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0.16</v>
+      </c>
+      <c r="AJ16">
+        <v>0.16</v>
+      </c>
+      <c r="AK16">
+        <v>0.16</v>
+      </c>
+      <c r="AL16">
+        <v>0.16</v>
       </c>
       <c r="AM16">
         <v>5.84</v>
@@ -2270,7 +2444,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2282,7 +2456,7 @@
         <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G17">
         <v>824315</v>
@@ -2341,17 +2515,23 @@
       <c r="Y17">
         <v>1.0231</v>
       </c>
+      <c r="Z17">
+        <v>4</v>
+      </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB17">
+        <v>1.1</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AD17">
         <v>5.6</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.2121</v>
@@ -2361,6 +2541,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-1.6</v>
+      </c>
+      <c r="AJ17">
+        <v>1.6</v>
+      </c>
+      <c r="AK17">
+        <v>-1.6</v>
+      </c>
+      <c r="AL17">
+        <v>1.6</v>
       </c>
       <c r="AM17">
         <v>5.6</v>
@@ -2371,7 +2563,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>2.5</v>
@@ -2383,7 +2575,7 @@
         <v>-110</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>824315</v>
@@ -2442,17 +2634,23 @@
       <c r="Y18">
         <v>0.88</v>
       </c>
+      <c r="Z18">
+        <v>2</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB18">
+        <v>-0.29</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD18">
         <v>2.21</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.1367</v>
@@ -2462,6 +2660,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>-0.21</v>
+      </c>
+      <c r="AJ18">
+        <v>0.21</v>
+      </c>
+      <c r="AK18">
+        <v>-0.21</v>
+      </c>
+      <c r="AL18">
+        <v>0.21</v>
       </c>
       <c r="AM18">
         <v>2.21</v>
@@ -2472,7 +2682,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2484,7 +2694,7 @@
         <v>112</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19">
         <v>824720</v>
@@ -2543,17 +2753,23 @@
       <c r="Y19">
         <v>1.0136</v>
       </c>
+      <c r="Z19">
+        <v>6</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>0.95</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>5.45</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.1953</v>
@@ -2563,6 +2779,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0.55</v>
+      </c>
+      <c r="AJ19">
+        <v>0.55</v>
+      </c>
+      <c r="AK19">
+        <v>0.55</v>
+      </c>
+      <c r="AL19">
+        <v>0.55</v>
       </c>
       <c r="AM19">
         <v>5.45</v>
@@ -2573,7 +2801,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>2.5</v>
@@ -2585,13 +2813,13 @@
         <v>-179</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>823909</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I20">
         <v>2.3</v>
@@ -2644,17 +2872,23 @@
       <c r="Y20">
         <v>0.9976</v>
       </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB20">
+        <v>0.07</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD20">
         <v>2.57</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.2551</v>
@@ -2664,6 +2898,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>-1.57</v>
+      </c>
+      <c r="AJ20">
+        <v>1.57</v>
+      </c>
+      <c r="AK20">
+        <v>-1.57</v>
+      </c>
+      <c r="AL20">
+        <v>1.57</v>
       </c>
       <c r="AM20">
         <v>2.57</v>
@@ -2674,7 +2920,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>8.5</v>
@@ -2686,7 +2932,7 @@
         <v>-110</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>823909</v>
@@ -2745,17 +2991,23 @@
       <c r="Y21">
         <v>1.0405</v>
       </c>
+      <c r="Z21">
+        <v>6</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB21">
+        <v>-1.05</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD21">
         <v>7.45</v>
       </c>
       <c r="AE21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AF21">
         <v>0.2902</v>
@@ -2765,6 +3017,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-1.45</v>
+      </c>
+      <c r="AJ21">
+        <v>1.45</v>
+      </c>
+      <c r="AK21">
+        <v>-1.45</v>
+      </c>
+      <c r="AL21">
+        <v>1.45</v>
       </c>
       <c r="AM21">
         <v>7.45</v>
@@ -2775,7 +3039,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2787,7 +3051,7 @@
         <v>-106</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G22">
         <v>823099</v>
@@ -2846,17 +3110,23 @@
       <c r="Y22">
         <v>0.972</v>
       </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB22">
+        <v>-0.27</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD22">
         <v>5.23</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2611</v>
@@ -2866,6 +3136,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-1.23</v>
+      </c>
+      <c r="AJ22">
+        <v>1.23</v>
+      </c>
+      <c r="AK22">
+        <v>-1.23</v>
+      </c>
+      <c r="AL22">
+        <v>1.23</v>
       </c>
       <c r="AM22">
         <v>5.23</v>
@@ -2876,7 +3158,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>5.5</v>
@@ -2888,7 +3170,7 @@
         <v>-165</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <v>823099</v>
@@ -2947,17 +3229,23 @@
       <c r="Y23">
         <v>0.941</v>
       </c>
+      <c r="Z23">
+        <v>5</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB23">
+        <v>-0.76</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>4.74</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.2315</v>
@@ -2967,6 +3255,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0.26</v>
+      </c>
+      <c r="AJ23">
+        <v>0.26</v>
+      </c>
+      <c r="AK23">
+        <v>0.26</v>
+      </c>
+      <c r="AL23">
+        <v>0.26</v>
       </c>
       <c r="AM23">
         <v>4.74</v>
@@ -2977,7 +3277,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -2989,7 +3289,7 @@
         <v>-105</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G24">
         <v>823258</v>
@@ -3048,17 +3348,23 @@
       <c r="Y24">
         <v>0.9918</v>
       </c>
+      <c r="Z24">
+        <v>3</v>
+      </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB24">
+        <v>-0.72</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD24">
         <v>2.78</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.1473</v>
@@ -3068,6 +3374,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0.22</v>
+      </c>
+      <c r="AJ24">
+        <v>0.22</v>
+      </c>
+      <c r="AK24">
+        <v>0.22</v>
+      </c>
+      <c r="AL24">
+        <v>0.22</v>
       </c>
       <c r="AM24">
         <v>2.78</v>
@@ -3078,7 +3396,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>3.5</v>
@@ -3090,7 +3408,7 @@
         <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G25">
         <v>823258</v>
@@ -3149,17 +3467,23 @@
       <c r="Y25">
         <v>0.9654</v>
       </c>
+      <c r="Z25">
+        <v>4</v>
+      </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>-0.3</v>
+      </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD25">
         <v>3.2</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.1815</v>
@@ -3169,6 +3493,18 @@
       </c>
       <c r="AH25">
         <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0.8</v>
+      </c>
+      <c r="AJ25">
+        <v>0.8</v>
+      </c>
+      <c r="AK25">
+        <v>0.8</v>
+      </c>
+      <c r="AL25">
+        <v>0.8</v>
       </c>
       <c r="AM25">
         <v>3.2</v>
@@ -3179,7 +3515,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>3.5</v>
@@ -3191,7 +3527,7 @@
         <v>-132</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G26">
         <v>825043</v>
@@ -3250,17 +3586,23 @@
       <c r="Y26">
         <v>0.88</v>
       </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
       <c r="AA26" t="s">
         <v>44</v>
       </c>
+      <c r="AB26">
+        <v>-0.61</v>
+      </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD26">
         <v>2.89</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF26">
         <v>0.1702</v>
@@ -3270,6 +3612,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>3.11</v>
+      </c>
+      <c r="AJ26">
+        <v>3.11</v>
+      </c>
+      <c r="AK26">
+        <v>3.11</v>
+      </c>
+      <c r="AL26">
+        <v>3.11</v>
       </c>
       <c r="AM26">
         <v>2.89</v>
@@ -3280,7 +3634,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3292,13 +3646,13 @@
         <v>134</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27">
         <v>825043</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I27">
         <v>4.4</v>
@@ -3351,17 +3705,23 @@
       <c r="Y27">
         <v>1.0765</v>
       </c>
+      <c r="Z27">
+        <v>3</v>
+      </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB27">
+        <v>2.05</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AD27">
         <v>5.55</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>0.1666</v>
@@ -3371,6 +3731,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>-2.55</v>
+      </c>
+      <c r="AJ27">
+        <v>2.55</v>
+      </c>
+      <c r="AK27">
+        <v>-2.55</v>
+      </c>
+      <c r="AL27">
+        <v>2.55</v>
       </c>
       <c r="AM27">
         <v>5.55</v>
@@ -3381,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3393,7 +3765,7 @@
         <v>-140</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28">
         <v>823745</v>
@@ -3452,17 +3824,23 @@
       <c r="Y28">
         <v>1.04</v>
       </c>
+      <c r="Z28">
+        <v>4</v>
+      </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB28">
+        <v>0.28</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD28">
         <v>5.78</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF28">
         <v>0.2442</v>
@@ -3472,6 +3850,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>-1.78</v>
+      </c>
+      <c r="AJ28">
+        <v>1.78</v>
+      </c>
+      <c r="AK28">
+        <v>-1.78</v>
+      </c>
+      <c r="AL28">
+        <v>1.78</v>
       </c>
       <c r="AM28">
         <v>5.78</v>
@@ -3482,7 +3872,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3494,7 +3884,7 @@
         <v>-112</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G29">
         <v>823745</v>
@@ -3553,17 +3943,23 @@
       <c r="Y29">
         <v>1.0258</v>
       </c>
+      <c r="Z29">
+        <v>5</v>
+      </c>
       <c r="AA29" t="s">
         <v>44</v>
       </c>
+      <c r="AB29">
+        <v>1.6</v>
+      </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD29">
         <v>6.1</v>
       </c>
       <c r="AE29" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AF29">
         <v>0.2438</v>
@@ -3573,6 +3969,18 @@
       </c>
       <c r="AH29">
         <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>-1.1</v>
+      </c>
+      <c r="AJ29">
+        <v>1.1</v>
+      </c>
+      <c r="AK29">
+        <v>-1.1</v>
+      </c>
+      <c r="AL29">
+        <v>1.1</v>
       </c>
       <c r="AM29">
         <v>6.1</v>
@@ -3583,7 +3991,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>6.5</v>
@@ -3595,31 +4003,31 @@
         <v>-108</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3627,7 +4035,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -3639,31 +4047,31 @@
         <v>-125</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3671,7 +4079,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>4.5</v>
@@ -3683,31 +4091,31 @@
         <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3715,7 +4123,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -3727,31 +4135,31 @@
         <v>-162</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L33">
         <v>6</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3759,7 +4167,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C34">
         <v>2.5</v>
@@ -3771,31 +4179,31 @@
         <v>-110</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L34">
         <v>3</v>
       </c>
       <c r="S34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE34" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
